--- a/Biobank, Collection, Network, Research Resource(v2.2).xlsx
+++ b/Biobank, Collection, Network, Research Resource(v2.2).xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30219"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gtrouli\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3F0AF2EE-610C-41FB-AB6B-86F5F75FFB99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12048" windowHeight="9048" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="sample,sample donor,event(v2.1)" sheetId="1" r:id="rId1"/>
@@ -18,7 +17,7 @@
     <sheet name="biobank,collection,etc(v2.2)" sheetId="3" r:id="rId3"/>
     <sheet name="triples(v2.2)" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1318" uniqueCount="686">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1626" uniqueCount="703">
   <si>
     <t>Entity</t>
   </si>
@@ -2296,83 +2295,134 @@
     <t>Adds field for DOI/Publications.</t>
   </si>
   <si>
-    <t>biobank 'has url' some 'biobank unique resource locator'</t>
-  </si>
-  <si>
-    <t>is contact information about' some 'collection or research resource contact role' (this class did not exist , now exists nad connected to biobank)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">collection or research resource contact role has identifier </t>
-  </si>
-  <si>
-    <t>has characteristic' some 'collection or research resource contact role'</t>
-  </si>
-  <si>
-    <t>has characteristic' some 'sample collection or study contact role'</t>
-  </si>
-  <si>
-    <t>is about' some 'collection or research resource aim description'</t>
-  </si>
-  <si>
-    <t>is about' some 'collection or research resource contact role'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">has biological sex' some 'biological sex' </t>
-  </si>
-  <si>
-    <t>collection or research resource contact role' 'has age'</t>
-  </si>
-  <si>
-    <t>collection or research resource contact role' ' has age unit'</t>
-  </si>
-  <si>
-    <t>has storage temperature' some 'storage temperature setting'</t>
-  </si>
-  <si>
-    <t>is about' 'collection or research resource contact role'</t>
-  </si>
-  <si>
-    <t>is about'  'collection or research resource contact role'</t>
-  </si>
-  <si>
-    <t>is about' some 'count of current total human study participant'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">network has identifier network ID </t>
-  </si>
-  <si>
-    <t>identifier and (designates some network)</t>
-  </si>
-  <si>
-    <t>network 'has url' some 'network unique resource locator'</t>
-  </si>
-  <si>
-    <t>part of' network</t>
-  </si>
-  <si>
-    <t>network is about country</t>
-  </si>
-  <si>
-    <t>is contact information about' some network</t>
-  </si>
-  <si>
-    <t>is about' some network</t>
-  </si>
-  <si>
-    <t>collection or research resource contact role 'has identifier' some 'research resource identifier'</t>
-  </si>
-  <si>
-    <t>has url' some 'research resource unique resource locator'</t>
-  </si>
-  <si>
-    <t>sample collection or study contact role' 'is about' some 'contact information'</t>
+    <t>http://purl.obolibrary.org/obo/OBIB_0000616</t>
+  </si>
+  <si>
+    <t>biobank</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/IAO_0020012</t>
+  </si>
+  <si>
+    <t>designates</t>
+  </si>
+  <si>
+    <t>biobank unique resource locator</t>
+  </si>
+  <si>
+    <t>has url</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is contact information about </t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002019</t>
+  </si>
+  <si>
+    <t>contact information</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/BFO_0000050</t>
+  </si>
+  <si>
+    <t>part of</t>
+  </si>
+  <si>
+    <t>has member</t>
+  </si>
+  <si>
+    <t>collection identifier</t>
+  </si>
+  <si>
+    <t>network type</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002039</t>
+  </si>
+  <si>
+    <t>has age unit</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0000671</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0000672</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">has age </t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002063</t>
+  </si>
+  <si>
+    <t>describes</t>
+  </si>
+  <si>
+    <t>has capability</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002064</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002065</t>
+  </si>
+  <si>
+    <t>conforms to</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002066</t>
+  </si>
+  <si>
+    <t>has location</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002068</t>
+  </si>
+  <si>
+    <t>included in</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002069</t>
+  </si>
+  <si>
+    <t>designed</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002070</t>
+  </si>
+  <si>
+    <t>governs</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002071</t>
+  </si>
+  <si>
+    <t>has status</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002072</t>
+  </si>
+  <si>
+    <t>has numbr of subjects</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is associated with </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="43">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="43" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2709,7 +2759,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2732,12 +2782,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -2886,7 +2930,6 @@
     <xf numFmtId="0" fontId="26" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1"/>
@@ -2950,6 +2993,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3230,31 +3274,31 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AD42"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" style="16" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" style="16" customWidth="1"/>
-    <col min="3" max="3" width="17.5703125" style="16" customWidth="1"/>
+    <col min="1" max="1" width="11.6640625" style="16" customWidth="1"/>
+    <col min="2" max="2" width="18.5546875" style="16" customWidth="1"/>
+    <col min="3" max="3" width="17.5546875" style="16" customWidth="1"/>
     <col min="4" max="4" width="15" style="16" customWidth="1"/>
-    <col min="5" max="5" width="15.85546875" style="16" customWidth="1"/>
-    <col min="6" max="6" width="23.7109375" style="16" customWidth="1"/>
-    <col min="7" max="7" width="37.7109375" style="16" customWidth="1"/>
-    <col min="8" max="8" width="44.7109375" style="16" customWidth="1"/>
+    <col min="5" max="5" width="15.88671875" style="16" customWidth="1"/>
+    <col min="6" max="6" width="23.6640625" style="16" customWidth="1"/>
+    <col min="7" max="7" width="37.6640625" style="16" customWidth="1"/>
+    <col min="8" max="8" width="44.6640625" style="16" customWidth="1"/>
     <col min="9" max="9" width="22" style="16" customWidth="1"/>
-    <col min="10" max="10" width="26.85546875" style="16" customWidth="1"/>
+    <col min="10" max="10" width="26.88671875" style="16" customWidth="1"/>
     <col min="11" max="11" width="86" style="16" customWidth="1"/>
     <col min="12" max="12" width="27" style="13" customWidth="1"/>
-    <col min="13" max="13" width="82.7109375" style="13" customWidth="1"/>
-    <col min="14" max="14" width="8.85546875" style="23"/>
+    <col min="13" max="13" width="82.6640625" style="13" customWidth="1"/>
+    <col min="14" max="14" width="8.88671875" style="23"/>
     <col min="15" max="15" width="27" style="13" customWidth="1"/>
-    <col min="16" max="20" width="8.85546875" style="16"/>
+    <col min="16" max="20" width="8.88671875" style="16"/>
     <col min="21" max="21" width="27" style="13" customWidth="1"/>
-    <col min="22" max="16384" width="8.85546875" style="16"/>
+    <col min="22" max="16384" width="8.88671875" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" s="10" customFormat="1" ht="15.6">
+    <row r="1" spans="1:30" s="10" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -3311,7 +3355,7 @@
       <c r="AC1" s="9"/>
       <c r="AD1" s="9"/>
     </row>
-    <row r="2" spans="1:30" ht="15.75">
+    <row r="2" spans="1:30" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>13</v>
       </c>
@@ -3353,7 +3397,7 @@
       <c r="AC2" s="15"/>
       <c r="AD2" s="15"/>
     </row>
-    <row r="3" spans="1:30" ht="15.75">
+    <row r="3" spans="1:30" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="25" t="s">
         <v>13</v>
       </c>
@@ -3410,7 +3454,7 @@
       <c r="AC3" s="18"/>
       <c r="AD3" s="18"/>
     </row>
-    <row r="4" spans="1:30" s="21" customFormat="1" ht="15.75">
+    <row r="4" spans="1:30" s="21" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="26" t="s">
         <v>13</v>
       </c>
@@ -3429,10 +3473,10 @@
       <c r="F4" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="72" t="s">
+      <c r="G4" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="73" t="s">
+      <c r="H4" s="72" t="s">
         <v>32</v>
       </c>
       <c r="I4" s="26" t="s">
@@ -3444,32 +3488,32 @@
       <c r="K4" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="L4" s="74" t="s">
+      <c r="L4" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="M4" s="74" t="s">
+      <c r="M4" s="73" t="s">
         <v>15</v>
       </c>
       <c r="N4" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="O4" s="74"/>
-      <c r="P4" s="75"/>
-      <c r="Q4" s="59"/>
-      <c r="R4" s="59"/>
-      <c r="S4" s="59"/>
-      <c r="T4" s="59"/>
-      <c r="U4" s="74"/>
-      <c r="V4" s="59"/>
-      <c r="W4" s="59"/>
-      <c r="X4" s="59"/>
-      <c r="Y4" s="76"/>
-      <c r="Z4" s="76"/>
-      <c r="AB4" s="76"/>
-      <c r="AC4" s="76"/>
-      <c r="AD4" s="76"/>
-    </row>
-    <row r="5" spans="1:30" ht="15.75">
+      <c r="O4" s="73"/>
+      <c r="P4" s="74"/>
+      <c r="Q4" s="58"/>
+      <c r="R4" s="58"/>
+      <c r="S4" s="58"/>
+      <c r="T4" s="58"/>
+      <c r="U4" s="73"/>
+      <c r="V4" s="58"/>
+      <c r="W4" s="58"/>
+      <c r="X4" s="58"/>
+      <c r="Y4" s="75"/>
+      <c r="Z4" s="75"/>
+      <c r="AB4" s="75"/>
+      <c r="AC4" s="75"/>
+      <c r="AD4" s="75"/>
+    </row>
+    <row r="5" spans="1:30" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="25" t="s">
         <v>13</v>
       </c>
@@ -3526,7 +3570,7 @@
       <c r="AC5" s="18"/>
       <c r="AD5" s="18"/>
     </row>
-    <row r="6" spans="1:30" ht="30.75">
+    <row r="6" spans="1:30" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="25" t="s">
         <v>13</v>
       </c>
@@ -3551,7 +3595,7 @@
       <c r="H6" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="I6" s="69" t="s">
+      <c r="I6" s="68" t="s">
         <v>50</v>
       </c>
       <c r="J6" s="25" t="s">
@@ -3584,7 +3628,7 @@
       <c r="AC6" s="3"/>
       <c r="AD6" s="3"/>
     </row>
-    <row r="7" spans="1:30">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A7" s="25" t="s">
         <v>13</v>
       </c>
@@ -3640,7 +3684,7 @@
       <c r="AC7" s="3"/>
       <c r="AD7" s="3"/>
     </row>
-    <row r="8" spans="1:30">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A8" s="25" t="s">
         <v>13</v>
       </c>
@@ -3696,7 +3740,7 @@
       <c r="AC8" s="3"/>
       <c r="AD8" s="3"/>
     </row>
-    <row r="9" spans="1:30">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A9" s="25" t="s">
         <v>13</v>
       </c>
@@ -3752,7 +3796,7 @@
       <c r="AC9" s="3"/>
       <c r="AD9" s="3"/>
     </row>
-    <row r="10" spans="1:30">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A10" s="25" t="s">
         <v>13</v>
       </c>
@@ -3808,7 +3852,7 @@
       <c r="AC10" s="3"/>
       <c r="AD10" s="3"/>
     </row>
-    <row r="11" spans="1:30">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A11" s="25" t="s">
         <v>13</v>
       </c>
@@ -3864,7 +3908,7 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
     </row>
-    <row r="12" spans="1:30">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A12" s="25" t="s">
         <v>13</v>
       </c>
@@ -3914,7 +3958,7 @@
       <c r="AC12" s="19"/>
       <c r="AD12" s="19"/>
     </row>
-    <row r="13" spans="1:30">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A13" s="25" t="s">
         <v>13</v>
       </c>
@@ -3972,7 +4016,7 @@
       <c r="AC13" s="3"/>
       <c r="AD13" s="3"/>
     </row>
-    <row r="14" spans="1:30" ht="15">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A14" s="25" t="s">
         <v>13</v>
       </c>
@@ -4030,7 +4074,7 @@
       <c r="AC14" s="3"/>
       <c r="AD14" s="3"/>
     </row>
-    <row r="15" spans="1:30" ht="15">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A15" s="25" t="s">
         <v>13</v>
       </c>
@@ -4082,7 +4126,7 @@
       <c r="AC15" s="3"/>
       <c r="AD15" s="3"/>
     </row>
-    <row r="16" spans="1:30" s="21" customFormat="1">
+    <row r="16" spans="1:30" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="26"/>
       <c r="B16" s="26"/>
       <c r="C16" s="26"/>
@@ -4114,7 +4158,7 @@
       <c r="AC16" s="17"/>
       <c r="AD16" s="17"/>
     </row>
-    <row r="17" spans="1:30">
+    <row r="17" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A17" s="28" t="s">
         <v>104</v>
       </c>
@@ -4159,7 +4203,7 @@
       <c r="AC17" s="3"/>
       <c r="AD17" s="3"/>
     </row>
-    <row r="18" spans="1:30">
+    <row r="18" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A18" s="25" t="s">
         <v>104</v>
       </c>
@@ -4212,7 +4256,7 @@
       <c r="AC18" s="3"/>
       <c r="AD18" s="3"/>
     </row>
-    <row r="19" spans="1:30" ht="15">
+    <row r="19" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A19" s="25" t="s">
         <v>104</v>
       </c>
@@ -4270,7 +4314,7 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
     </row>
-    <row r="20" spans="1:30">
+    <row r="20" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A20" s="25" t="s">
         <v>104</v>
       </c>
@@ -4326,7 +4370,7 @@
       <c r="AC20" s="19"/>
       <c r="AD20" s="19"/>
     </row>
-    <row r="21" spans="1:30" ht="53.25">
+    <row r="21" spans="1:30" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A21" s="25" t="s">
         <v>104</v>
       </c>
@@ -4339,7 +4383,7 @@
       <c r="D21" s="25" t="s">
         <v>134</v>
       </c>
-      <c r="E21" s="70" t="s">
+      <c r="E21" s="69" t="s">
         <v>135</v>
       </c>
       <c r="F21" s="25" t="s">
@@ -4351,13 +4395,13 @@
       <c r="H21" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I21" s="68" t="s">
+      <c r="I21" s="67" t="s">
         <v>138</v>
       </c>
       <c r="J21" s="25" t="s">
         <v>139</v>
       </c>
-      <c r="K21" s="71" t="s">
+      <c r="K21" s="70" t="s">
         <v>140</v>
       </c>
       <c r="L21" s="13" t="s">
@@ -4384,7 +4428,7 @@
       <c r="AC21" s="3"/>
       <c r="AD21" s="3"/>
     </row>
-    <row r="22" spans="1:30" ht="15">
+    <row r="22" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -4412,7 +4456,7 @@
       <c r="AC22" s="3"/>
       <c r="AD22" s="3"/>
     </row>
-    <row r="23" spans="1:30" ht="15">
+    <row r="23" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>142</v>
       </c>
@@ -4453,7 +4497,7 @@
       <c r="AC23" s="3"/>
       <c r="AD23" s="3"/>
     </row>
-    <row r="24" spans="1:30" ht="15">
+    <row r="24" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>142</v>
       </c>
@@ -4504,7 +4548,7 @@
       <c r="AC24" s="3"/>
       <c r="AD24" s="3"/>
     </row>
-    <row r="25" spans="1:30" ht="15">
+    <row r="25" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>142</v>
       </c>
@@ -4558,7 +4602,7 @@
       <c r="AC25" s="3"/>
       <c r="AD25" s="3"/>
     </row>
-    <row r="26" spans="1:30" ht="15">
+    <row r="26" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>142</v>
       </c>
@@ -4612,7 +4656,7 @@
       <c r="AC26" s="3"/>
       <c r="AD26" s="3"/>
     </row>
-    <row r="27" spans="1:30" ht="15">
+    <row r="27" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>142</v>
       </c>
@@ -4668,89 +4712,89 @@
       <c r="AC27" s="3"/>
       <c r="AD27" s="3"/>
     </row>
-    <row r="28" spans="1:30">
+    <row r="28" spans="1:30" x14ac:dyDescent="0.3">
       <c r="G28" s="11"/>
       <c r="H28" s="11"/>
       <c r="J28" s="3"/>
       <c r="N28" s="3"/>
     </row>
-    <row r="29" spans="1:30">
+    <row r="29" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B29" s="19"/>
       <c r="J29" s="3"/>
       <c r="N29" s="3"/>
     </row>
-    <row r="30" spans="1:30">
+    <row r="30" spans="1:30" x14ac:dyDescent="0.3">
       <c r="J30" s="3"/>
       <c r="N30" s="3"/>
     </row>
-    <row r="31" spans="1:30">
+    <row r="31" spans="1:30" x14ac:dyDescent="0.3">
       <c r="J31" s="3"/>
       <c r="N31" s="3"/>
     </row>
-    <row r="32" spans="1:30">
+    <row r="32" spans="1:30" x14ac:dyDescent="0.3">
       <c r="J32" s="3"/>
       <c r="N32" s="3"/>
     </row>
-    <row r="33" spans="10:14">
+    <row r="33" spans="10:14" x14ac:dyDescent="0.3">
       <c r="J33" s="3"/>
       <c r="N33" s="3"/>
     </row>
-    <row r="34" spans="10:14">
+    <row r="34" spans="10:14" x14ac:dyDescent="0.3">
       <c r="J34" s="3"/>
       <c r="N34" s="3"/>
     </row>
-    <row r="35" spans="10:14">
+    <row r="35" spans="10:14" x14ac:dyDescent="0.3">
       <c r="J35" s="3"/>
       <c r="N35" s="3"/>
     </row>
-    <row r="36" spans="10:14">
+    <row r="36" spans="10:14" x14ac:dyDescent="0.3">
       <c r="J36" s="3"/>
       <c r="N36" s="3"/>
     </row>
-    <row r="37" spans="10:14">
+    <row r="37" spans="10:14" x14ac:dyDescent="0.3">
       <c r="J37" s="3"/>
       <c r="N37" s="3"/>
     </row>
-    <row r="38" spans="10:14">
+    <row r="38" spans="10:14" x14ac:dyDescent="0.3">
       <c r="J38" s="3"/>
       <c r="N38" s="3"/>
     </row>
-    <row r="39" spans="10:14">
+    <row r="39" spans="10:14" x14ac:dyDescent="0.3">
       <c r="J39" s="3"/>
       <c r="N39" s="3"/>
     </row>
-    <row r="40" spans="10:14">
+    <row r="40" spans="10:14" x14ac:dyDescent="0.3">
       <c r="J40" s="3"/>
       <c r="N40" s="3"/>
     </row>
-    <row r="41" spans="10:14">
+    <row r="41" spans="10:14" x14ac:dyDescent="0.3">
       <c r="J41" s="3"/>
       <c r="N41" s="3"/>
     </row>
-    <row r="42" spans="10:14">
+    <row r="42" spans="10:14" x14ac:dyDescent="0.3">
       <c r="J42" s="3"/>
       <c r="N42" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="G3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="G5" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="H6" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="H7" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="H13" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="H14" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="H15" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="G17" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="H18" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="G21" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="H23" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="H24" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="H25" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="H26" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="H27" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="K20" r:id="rId17" display="http://purl.obolibrary.org/obo/IAO_0000030" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="K21" r:id="rId18" display="http://purl.obolibrary.org/obo/OBIB_0000482" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="G2" r:id="rId1"/>
+    <hyperlink ref="G3" r:id="rId2"/>
+    <hyperlink ref="G5" r:id="rId3"/>
+    <hyperlink ref="H6" r:id="rId4"/>
+    <hyperlink ref="H7" r:id="rId5"/>
+    <hyperlink ref="H13" r:id="rId6"/>
+    <hyperlink ref="H14" r:id="rId7"/>
+    <hyperlink ref="H15" r:id="rId8"/>
+    <hyperlink ref="G17" r:id="rId9"/>
+    <hyperlink ref="H18" r:id="rId10"/>
+    <hyperlink ref="G21" r:id="rId11"/>
+    <hyperlink ref="H23" r:id="rId12"/>
+    <hyperlink ref="H24" r:id="rId13"/>
+    <hyperlink ref="H25" r:id="rId14"/>
+    <hyperlink ref="H26" r:id="rId15"/>
+    <hyperlink ref="H27" r:id="rId16"/>
+    <hyperlink ref="K20" r:id="rId17" display="http://purl.obolibrary.org/obo/IAO_0000030"/>
+    <hyperlink ref="K21" r:id="rId18" display="http://purl.obolibrary.org/obo/OBIB_0000482"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId19"/>
@@ -4758,19 +4802,19 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G33"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.28515625" customWidth="1"/>
+    <col min="1" max="1" width="21.33203125" customWidth="1"/>
     <col min="2" max="2" width="49" customWidth="1"/>
-    <col min="3" max="3" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="53.7109375" customWidth="1"/>
-    <col min="5" max="5" width="31.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="37.85546875" customWidth="1"/>
+    <col min="3" max="3" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="53.6640625" customWidth="1"/>
+    <col min="5" max="5" width="31.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="37.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="10" customFormat="1">
+    <row r="1" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>173</v>
       </c>
@@ -4790,7 +4834,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -4810,7 +4854,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -4830,7 +4874,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -4850,7 +4894,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -4870,7 +4914,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>58</v>
       </c>
@@ -4890,7 +4934,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>58</v>
       </c>
@@ -4910,7 +4954,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>58</v>
       </c>
@@ -4930,7 +4974,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>58</v>
       </c>
@@ -4950,7 +4994,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -4970,7 +5014,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -4990,7 +5034,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -5010,12 +5054,12 @@
         <v>101</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B13" s="11"/>
       <c r="D13" s="11"/>
       <c r="F13" s="11"/>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>106</v>
       </c>
@@ -5035,7 +5079,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>106</v>
       </c>
@@ -5055,7 +5099,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>106</v>
       </c>
@@ -5075,7 +5119,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>106</v>
       </c>
@@ -5098,7 +5142,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>106</v>
       </c>
@@ -5119,11 +5163,11 @@
       </c>
       <c r="G18" s="2"/>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B19" s="11"/>
       <c r="D19" s="11"/>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>151</v>
       </c>
@@ -5143,7 +5187,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>206</v>
       </c>
@@ -5163,7 +5207,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>206</v>
       </c>
@@ -5183,7 +5227,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>206</v>
       </c>
@@ -5203,78 +5247,78 @@
         <v>170</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B24" s="11"/>
       <c r="D24" s="11"/>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B25" s="11"/>
       <c r="D25" s="11"/>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D26" s="11"/>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D27" s="11"/>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D28" s="11"/>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D29" s="11"/>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D30" s="11"/>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D31" s="11"/>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D32" s="11"/>
     </row>
-    <row r="33" spans="4:4">
+    <row r="33" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D33" s="11"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
-    <hyperlink ref="B2" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
-    <hyperlink ref="B14" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
-    <hyperlink ref="F20" r:id="rId4" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
-    <hyperlink ref="B20" r:id="rId5" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
-    <hyperlink ref="F14" r:id="rId6" xr:uid="{00000000-0004-0000-0100-000005000000}"/>
-    <hyperlink ref="F21" r:id="rId7" xr:uid="{00000000-0004-0000-0100-000006000000}"/>
-    <hyperlink ref="F22" r:id="rId8" xr:uid="{00000000-0004-0000-0100-000007000000}"/>
-    <hyperlink ref="F23" r:id="rId9" xr:uid="{00000000-0004-0000-0100-000008000000}"/>
-    <hyperlink ref="F4" r:id="rId10" xr:uid="{00000000-0004-0000-0100-000009000000}"/>
-    <hyperlink ref="F5" r:id="rId11" xr:uid="{00000000-0004-0000-0100-00000A000000}"/>
-    <hyperlink ref="F3" r:id="rId12" xr:uid="{00000000-0004-0000-0100-00000B000000}"/>
-    <hyperlink ref="F6" r:id="rId13" xr:uid="{00000000-0004-0000-0100-00000C000000}"/>
-    <hyperlink ref="F7" r:id="rId14" xr:uid="{00000000-0004-0000-0100-00000D000000}"/>
-    <hyperlink ref="F8" r:id="rId15" xr:uid="{00000000-0004-0000-0100-00000E000000}"/>
-    <hyperlink ref="F9" r:id="rId16" xr:uid="{00000000-0004-0000-0100-00000F000000}"/>
-    <hyperlink ref="B6" r:id="rId17" xr:uid="{00000000-0004-0000-0100-000010000000}"/>
-    <hyperlink ref="B7" r:id="rId18" display="http://purl.obolibrary.org/obo/obib.owl/OBIB_0002017" xr:uid="{00000000-0004-0000-0100-000011000000}"/>
-    <hyperlink ref="B8" r:id="rId19" display="http://purl.obolibrary.org/obo/obib.owl/OBIB_0002017" xr:uid="{00000000-0004-0000-0100-000012000000}"/>
-    <hyperlink ref="B9" r:id="rId20" display="http://purl.obolibrary.org/obo/obib.owl/OBIB_0002017" xr:uid="{00000000-0004-0000-0100-000013000000}"/>
-    <hyperlink ref="F10" r:id="rId21" xr:uid="{00000000-0004-0000-0100-000014000000}"/>
-    <hyperlink ref="F11" r:id="rId22" xr:uid="{00000000-0004-0000-0100-000015000000}"/>
-    <hyperlink ref="F12" r:id="rId23" xr:uid="{00000000-0004-0000-0100-000016000000}"/>
-    <hyperlink ref="F16" r:id="rId24" xr:uid="{00000000-0004-0000-0100-000017000000}"/>
-    <hyperlink ref="B15" r:id="rId25" xr:uid="{00000000-0004-0000-0100-000018000000}"/>
-    <hyperlink ref="B16" r:id="rId26" xr:uid="{00000000-0004-0000-0100-000019000000}"/>
-    <hyperlink ref="B17" r:id="rId27" xr:uid="{00000000-0004-0000-0100-00001A000000}"/>
-    <hyperlink ref="B3" r:id="rId28" xr:uid="{00000000-0004-0000-0100-00001B000000}"/>
-    <hyperlink ref="B4" r:id="rId29" xr:uid="{00000000-0004-0000-0100-00001C000000}"/>
-    <hyperlink ref="B5" r:id="rId30" xr:uid="{00000000-0004-0000-0100-00001D000000}"/>
-    <hyperlink ref="B10" r:id="rId31" xr:uid="{00000000-0004-0000-0100-00001E000000}"/>
-    <hyperlink ref="B11" r:id="rId32" xr:uid="{00000000-0004-0000-0100-00001F000000}"/>
-    <hyperlink ref="B12" r:id="rId33" xr:uid="{00000000-0004-0000-0100-000020000000}"/>
-    <hyperlink ref="B21" r:id="rId34" xr:uid="{00000000-0004-0000-0100-000021000000}"/>
-    <hyperlink ref="B22" r:id="rId35" xr:uid="{00000000-0004-0000-0100-000022000000}"/>
-    <hyperlink ref="B23" r:id="rId36" xr:uid="{00000000-0004-0000-0100-000023000000}"/>
-    <hyperlink ref="D14" r:id="rId37" xr:uid="{00000000-0004-0000-0100-000024000000}"/>
-    <hyperlink ref="F17" r:id="rId38" xr:uid="{00000000-0004-0000-0100-000025000000}"/>
+    <hyperlink ref="F2" r:id="rId1"/>
+    <hyperlink ref="B2" r:id="rId2"/>
+    <hyperlink ref="B14" r:id="rId3"/>
+    <hyperlink ref="F20" r:id="rId4"/>
+    <hyperlink ref="B20" r:id="rId5"/>
+    <hyperlink ref="F14" r:id="rId6"/>
+    <hyperlink ref="F21" r:id="rId7"/>
+    <hyperlink ref="F22" r:id="rId8"/>
+    <hyperlink ref="F23" r:id="rId9"/>
+    <hyperlink ref="F4" r:id="rId10"/>
+    <hyperlink ref="F5" r:id="rId11"/>
+    <hyperlink ref="F3" r:id="rId12"/>
+    <hyperlink ref="F6" r:id="rId13"/>
+    <hyperlink ref="F7" r:id="rId14"/>
+    <hyperlink ref="F8" r:id="rId15"/>
+    <hyperlink ref="F9" r:id="rId16"/>
+    <hyperlink ref="B6" r:id="rId17"/>
+    <hyperlink ref="B7" r:id="rId18" display="http://purl.obolibrary.org/obo/obib.owl/OBIB_0002017"/>
+    <hyperlink ref="B8" r:id="rId19" display="http://purl.obolibrary.org/obo/obib.owl/OBIB_0002017"/>
+    <hyperlink ref="B9" r:id="rId20" display="http://purl.obolibrary.org/obo/obib.owl/OBIB_0002017"/>
+    <hyperlink ref="F10" r:id="rId21"/>
+    <hyperlink ref="F11" r:id="rId22"/>
+    <hyperlink ref="F12" r:id="rId23"/>
+    <hyperlink ref="F16" r:id="rId24"/>
+    <hyperlink ref="B15" r:id="rId25"/>
+    <hyperlink ref="B16" r:id="rId26"/>
+    <hyperlink ref="B17" r:id="rId27"/>
+    <hyperlink ref="B3" r:id="rId28"/>
+    <hyperlink ref="B4" r:id="rId29"/>
+    <hyperlink ref="B5" r:id="rId30"/>
+    <hyperlink ref="B10" r:id="rId31"/>
+    <hyperlink ref="B11" r:id="rId32"/>
+    <hyperlink ref="B12" r:id="rId33"/>
+    <hyperlink ref="B21" r:id="rId34"/>
+    <hyperlink ref="B22" r:id="rId35"/>
+    <hyperlink ref="B23" r:id="rId36"/>
+    <hyperlink ref="D14" r:id="rId37"/>
+    <hyperlink ref="F17" r:id="rId38"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId39"/>
@@ -5282,26 +5326,26 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AD142"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" customWidth="1"/>
-    <col min="2" max="2" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="40.85546875" customWidth="1"/>
-    <col min="5" max="5" width="41.42578125" customWidth="1"/>
-    <col min="6" max="6" width="79.42578125" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="40.88671875" customWidth="1"/>
+    <col min="5" max="5" width="41.44140625" customWidth="1"/>
+    <col min="6" max="6" width="79.44140625" customWidth="1"/>
     <col min="7" max="7" width="33" customWidth="1"/>
-    <col min="8" max="8" width="47.7109375" customWidth="1"/>
-    <col min="9" max="9" width="51.5703125" customWidth="1"/>
-    <col min="10" max="10" width="74.42578125" customWidth="1"/>
-    <col min="11" max="11" width="100.28515625" customWidth="1"/>
-    <col min="12" max="12" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="47.6640625" customWidth="1"/>
+    <col min="9" max="9" width="51.5546875" customWidth="1"/>
+    <col min="10" max="10" width="74.44140625" customWidth="1"/>
+    <col min="11" max="11" width="100.33203125" customWidth="1"/>
+    <col min="12" max="12" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" s="10" customFormat="1" ht="15.6">
+    <row r="1" spans="1:30" s="10" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
@@ -5358,7 +5402,7 @@
       <c r="AC1" s="9"/>
       <c r="AD1" s="9"/>
     </row>
-    <row r="2" spans="1:30">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>218</v>
       </c>
@@ -5377,7 +5421,7 @@
       <c r="L2" s="32"/>
       <c r="M2" s="32"/>
     </row>
-    <row r="3" spans="1:30">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A3" s="32" t="s">
         <v>218</v>
       </c>
@@ -5414,7 +5458,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="4" spans="1:30">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A4" s="32" t="s">
         <v>218</v>
       </c>
@@ -5449,7 +5493,7 @@
       <c r="L4" s="32"/>
       <c r="M4" s="32"/>
     </row>
-    <row r="5" spans="1:30">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A5" s="32" t="s">
         <v>218</v>
       </c>
@@ -5484,7 +5528,7 @@
       <c r="L5" s="32"/>
       <c r="M5" s="32"/>
     </row>
-    <row r="6" spans="1:30">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A6" s="32" t="s">
         <v>218</v>
       </c>
@@ -5519,7 +5563,7 @@
       <c r="L6" s="32"/>
       <c r="M6" s="32"/>
     </row>
-    <row r="7" spans="1:30">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A7" s="32" t="s">
         <v>218</v>
       </c>
@@ -5554,7 +5598,7 @@
       <c r="L7" s="32"/>
       <c r="M7" s="32"/>
     </row>
-    <row r="8" spans="1:30">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A8" s="32" t="s">
         <v>218</v>
       </c>
@@ -5591,7 +5635,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="9" spans="1:30">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A9" s="32" t="s">
         <v>218</v>
       </c>
@@ -5628,7 +5672,7 @@
       </c>
       <c r="M9" s="32"/>
     </row>
-    <row r="10" spans="1:30">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A10" s="32" t="s">
         <v>218</v>
       </c>
@@ -5665,7 +5709,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="11" spans="1:30">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A11" s="32" t="s">
         <v>218</v>
       </c>
@@ -5704,7 +5748,7 @@
       </c>
       <c r="M11" s="32"/>
     </row>
-    <row r="12" spans="1:30" ht="15">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A12" s="32" t="s">
         <v>218</v>
       </c>
@@ -5743,7 +5787,7 @@
       </c>
       <c r="M12" s="32"/>
     </row>
-    <row r="13" spans="1:30">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A13" s="32" t="s">
         <v>218</v>
       </c>
@@ -5782,7 +5826,7 @@
       </c>
       <c r="M13" s="32"/>
     </row>
-    <row r="14" spans="1:30" s="32" customFormat="1" ht="15">
+    <row r="14" spans="1:30" s="32" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="32" t="s">
         <v>218</v>
       </c>
@@ -5823,7 +5867,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="15" spans="1:30" ht="15">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A15" s="33" t="s">
         <v>318</v>
       </c>
@@ -5848,7 +5892,7 @@
       <c r="L15" s="32"/>
       <c r="M15" s="32"/>
     </row>
-    <row r="16" spans="1:30">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A16" s="32" t="s">
         <v>318</v>
       </c>
@@ -5885,7 +5929,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="24">
+    <row r="17" spans="1:13" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="32" t="s">
         <v>318</v>
       </c>
@@ -5920,7 +5964,7 @@
       <c r="L17" s="32"/>
       <c r="M17" s="32"/>
     </row>
-    <row r="18" spans="1:13" ht="24">
+    <row r="18" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="32" t="s">
         <v>318</v>
       </c>
@@ -5946,7 +5990,7 @@
       <c r="I18" s="32" t="s">
         <v>334</v>
       </c>
-      <c r="J18" s="65" t="s">
+      <c r="J18" s="64" t="s">
         <v>335</v>
       </c>
       <c r="K18" s="38" t="s">
@@ -5955,7 +5999,7 @@
       <c r="L18" s="32"/>
       <c r="M18" s="32"/>
     </row>
-    <row r="19" spans="1:13" ht="15">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="32" t="s">
         <v>318</v>
       </c>
@@ -5992,46 +6036,46 @@
       <c r="L19" s="32"/>
       <c r="M19" s="32"/>
     </row>
-    <row r="20" spans="1:13" s="48" customFormat="1" ht="15">
-      <c r="A20" s="45" t="s">
+    <row r="20" spans="1:13" s="47" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="44" t="s">
         <v>318</v>
       </c>
-      <c r="B20" s="45" t="s">
+      <c r="B20" s="44" t="s">
         <v>346</v>
       </c>
-      <c r="C20" s="45" t="s">
+      <c r="C20" s="44" t="s">
         <v>268</v>
       </c>
-      <c r="D20" s="45" t="s">
+      <c r="D20" s="44" t="s">
         <v>269</v>
       </c>
-      <c r="E20" s="45" t="s">
+      <c r="E20" s="44" t="s">
         <v>347</v>
       </c>
-      <c r="F20" s="45" t="s">
+      <c r="F20" s="44" t="s">
         <v>348</v>
       </c>
-      <c r="G20" s="45" t="s">
+      <c r="G20" s="44" t="s">
         <v>289</v>
       </c>
-      <c r="H20" s="46" t="s">
+      <c r="H20" s="45" t="s">
         <v>272</v>
       </c>
-      <c r="I20" s="45" t="s">
+      <c r="I20" s="44" t="s">
         <v>273</v>
       </c>
-      <c r="J20" s="47" t="s">
+      <c r="J20" s="46" t="s">
         <v>349</v>
       </c>
       <c r="K20" s="26" t="s">
         <v>350</v>
       </c>
-      <c r="L20" s="45" t="s">
+      <c r="L20" s="44" t="s">
         <v>351</v>
       </c>
-      <c r="M20" s="45"/>
-    </row>
-    <row r="21" spans="1:13">
+      <c r="M20" s="44"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="32" t="s">
         <v>318</v>
       </c>
@@ -6068,7 +6112,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="32" t="s">
         <v>318</v>
       </c>
@@ -6105,7 +6149,7 @@
       </c>
       <c r="M22" s="32"/>
     </row>
-    <row r="23" spans="1:13" ht="24">
+    <row r="23" spans="1:13" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="32" t="s">
         <v>318</v>
       </c>
@@ -6142,7 +6186,7 @@
       </c>
       <c r="M23" s="32"/>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="32" t="s">
         <v>318</v>
       </c>
@@ -6179,7 +6223,7 @@
       <c r="L24" s="32"/>
       <c r="M24" s="32"/>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="32" t="s">
         <v>318</v>
       </c>
@@ -6216,7 +6260,7 @@
       <c r="L25" s="32"/>
       <c r="M25" s="32"/>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="32" t="s">
         <v>318</v>
       </c>
@@ -6255,46 +6299,46 @@
       </c>
       <c r="M26" s="32"/>
     </row>
-    <row r="27" spans="1:13" s="48" customFormat="1" ht="15">
-      <c r="A27" s="45" t="s">
+    <row r="27" spans="1:13" s="47" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="44" t="s">
         <v>318</v>
       </c>
-      <c r="B27" s="45" t="s">
+      <c r="B27" s="44" t="s">
         <v>390</v>
       </c>
-      <c r="C27" s="45" t="s">
+      <c r="C27" s="44" t="s">
         <v>391</v>
       </c>
-      <c r="D27" s="45" t="s">
+      <c r="D27" s="44" t="s">
         <v>392</v>
       </c>
-      <c r="E27" s="45" t="s">
+      <c r="E27" s="44" t="s">
         <v>393</v>
       </c>
-      <c r="F27" s="45" t="s">
+      <c r="F27" s="44" t="s">
         <v>394</v>
       </c>
-      <c r="G27" s="45" t="s">
+      <c r="G27" s="44" t="s">
         <v>289</v>
       </c>
-      <c r="H27" s="46" t="s">
+      <c r="H27" s="45" t="s">
         <v>395</v>
       </c>
-      <c r="I27" s="45" t="s">
+      <c r="I27" s="44" t="s">
         <v>396</v>
       </c>
-      <c r="J27" s="45" t="s">
+      <c r="J27" s="44" t="s">
         <v>393</v>
       </c>
       <c r="K27" s="26" t="s">
         <v>345</v>
       </c>
-      <c r="L27" s="45" t="s">
+      <c r="L27" s="44" t="s">
         <v>389</v>
       </c>
-      <c r="M27" s="45"/>
-    </row>
-    <row r="28" spans="1:13" ht="15">
+      <c r="M27" s="44"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="32" t="s">
         <v>318</v>
       </c>
@@ -6322,7 +6366,7 @@
       <c r="I28" s="32" t="s">
         <v>402</v>
       </c>
-      <c r="K28" s="44" t="s">
+      <c r="K28" s="43" t="s">
         <v>403</v>
       </c>
       <c r="L28" s="32" t="s">
@@ -6330,7 +6374,7 @@
       </c>
       <c r="M28" s="32"/>
     </row>
-    <row r="29" spans="1:13" ht="15">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="32" t="s">
         <v>318</v>
       </c>
@@ -6367,44 +6411,44 @@
       </c>
       <c r="M29" s="32"/>
     </row>
-    <row r="30" spans="1:13" s="48" customFormat="1" ht="15" customHeight="1">
-      <c r="A30" s="45" t="s">
+    <row r="30" spans="1:13" s="47" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="44" t="s">
         <v>318</v>
       </c>
-      <c r="B30" s="45" t="s">
+      <c r="B30" s="44" t="s">
         <v>411</v>
       </c>
-      <c r="C30" s="45" t="s">
+      <c r="C30" s="44" t="s">
         <v>412</v>
       </c>
-      <c r="D30" s="45" t="s">
+      <c r="D30" s="44" t="s">
         <v>413</v>
       </c>
-      <c r="E30" s="45" t="s">
+      <c r="E30" s="44" t="s">
         <v>414</v>
       </c>
-      <c r="F30" s="45" t="s">
+      <c r="F30" s="44" t="s">
         <v>415</v>
       </c>
-      <c r="G30" s="46" t="s">
+      <c r="G30" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="H30" s="45"/>
-      <c r="I30" s="45" t="s">
+      <c r="H30" s="44"/>
+      <c r="I30" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="J30" s="62" t="s">
+      <c r="J30" s="61" t="s">
         <v>42</v>
       </c>
-      <c r="K30" s="47" t="s">
+      <c r="K30" s="46" t="s">
         <v>368</v>
       </c>
-      <c r="L30" s="45" t="s">
+      <c r="L30" s="44" t="s">
         <v>416</v>
       </c>
-      <c r="M30" s="45"/>
-    </row>
-    <row r="31" spans="1:13" ht="15">
+      <c r="M30" s="44"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="32" t="s">
         <v>318</v>
       </c>
@@ -6430,7 +6474,7 @@
       <c r="I31" s="32" t="s">
         <v>423</v>
       </c>
-      <c r="J31" s="62" t="s">
+      <c r="J31" s="61" t="s">
         <v>424</v>
       </c>
       <c r="K31" s="38" t="s">
@@ -6441,7 +6485,7 @@
       </c>
       <c r="M31" s="32"/>
     </row>
-    <row r="32" spans="1:13" ht="15">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="32" t="s">
         <v>318</v>
       </c>
@@ -6469,7 +6513,7 @@
       <c r="I32" s="32" t="s">
         <v>431</v>
       </c>
-      <c r="J32" s="62" t="s">
+      <c r="J32" s="61" t="s">
         <v>428</v>
       </c>
       <c r="K32" s="25" t="s">
@@ -6480,7 +6524,7 @@
       </c>
       <c r="M32" s="32"/>
     </row>
-    <row r="33" spans="1:13">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="32" t="s">
         <v>318</v>
       </c>
@@ -6519,46 +6563,46 @@
       </c>
       <c r="M33" s="32"/>
     </row>
-    <row r="34" spans="1:13" s="48" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A34" s="45" t="s">
+    <row r="34" spans="1:13" s="47" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="44" t="s">
         <v>318</v>
       </c>
-      <c r="B34" s="45" t="s">
+      <c r="B34" s="44" t="s">
         <v>441</v>
       </c>
-      <c r="C34" s="45" t="s">
+      <c r="C34" s="44" t="s">
         <v>53</v>
       </c>
-      <c r="D34" s="45" t="s">
+      <c r="D34" s="44" t="s">
         <v>92</v>
       </c>
-      <c r="E34" s="45" t="s">
+      <c r="E34" s="44" t="s">
         <v>442</v>
       </c>
-      <c r="F34" s="45" t="s">
+      <c r="F34" s="44" t="s">
         <v>443</v>
       </c>
-      <c r="G34" s="45" t="s">
+      <c r="G34" s="44" t="s">
         <v>289</v>
       </c>
-      <c r="H34" s="46" t="s">
+      <c r="H34" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="I34" s="45" t="s">
+      <c r="I34" s="44" t="s">
         <v>444</v>
       </c>
-      <c r="J34" s="63" t="s">
+      <c r="J34" s="62" t="s">
         <v>93</v>
       </c>
       <c r="K34" s="26" t="s">
         <v>345</v>
       </c>
-      <c r="L34" s="45" t="s">
+      <c r="L34" s="44" t="s">
         <v>445</v>
       </c>
-      <c r="M34" s="45"/>
-    </row>
-    <row r="35" spans="1:13">
+      <c r="M34" s="44"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="32" t="s">
         <v>318</v>
       </c>
@@ -6597,7 +6641,7 @@
       </c>
       <c r="M35" s="32"/>
     </row>
-    <row r="36" spans="1:13" ht="30.75">
+    <row r="36" spans="1:13" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="32" t="s">
         <v>318</v>
       </c>
@@ -6623,7 +6667,7 @@
       <c r="I36" s="32" t="s">
         <v>460</v>
       </c>
-      <c r="J36" s="56" t="s">
+      <c r="J36" s="55" t="s">
         <v>461</v>
       </c>
       <c r="K36" s="38" t="s">
@@ -6632,7 +6676,7 @@
       <c r="L36" s="32"/>
       <c r="M36" s="32"/>
     </row>
-    <row r="37" spans="1:13" ht="15">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="32" t="s">
         <v>318</v>
       </c>
@@ -6669,7 +6713,7 @@
       </c>
       <c r="M37" s="32"/>
     </row>
-    <row r="38" spans="1:13" ht="15" thickBot="1">
+    <row r="38" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="32" t="s">
         <v>318</v>
       </c>
@@ -6708,7 +6752,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="15" customHeight="1" thickBot="1">
+    <row r="39" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="42" t="s">
         <v>480</v>
       </c>
@@ -6733,7 +6777,7 @@
       <c r="L39" s="32"/>
       <c r="M39" s="32"/>
     </row>
-    <row r="40" spans="1:13">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" s="32" t="s">
         <v>480</v>
       </c>
@@ -6772,7 +6816,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="30.75">
+    <row r="41" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A41" s="32" t="s">
         <v>480</v>
       </c>
@@ -6800,7 +6844,7 @@
       <c r="I41" s="32" t="s">
         <v>497</v>
       </c>
-      <c r="J41" s="56" t="s">
+      <c r="J41" s="55" t="s">
         <v>498</v>
       </c>
       <c r="K41" s="38" t="s">
@@ -6809,7 +6853,7 @@
       <c r="L41" s="32"/>
       <c r="M41" s="32"/>
     </row>
-    <row r="42" spans="1:13" ht="30.75">
+    <row r="42" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A42" s="32" t="s">
         <v>480</v>
       </c>
@@ -6837,7 +6881,7 @@
       <c r="I42" s="32" t="s">
         <v>497</v>
       </c>
-      <c r="J42" s="56" t="s">
+      <c r="J42" s="55" t="s">
         <v>498</v>
       </c>
       <c r="K42" s="38" t="s">
@@ -6846,7 +6890,7 @@
       <c r="L42" s="32"/>
       <c r="M42" s="32"/>
     </row>
-    <row r="43" spans="1:13">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" s="32" t="s">
         <v>480</v>
       </c>
@@ -6883,7 +6927,7 @@
       <c r="L43" s="32"/>
       <c r="M43" s="32"/>
     </row>
-    <row r="44" spans="1:13" ht="15">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" s="32" t="s">
         <v>480</v>
       </c>
@@ -6920,7 +6964,7 @@
       <c r="L44" s="32"/>
       <c r="M44" s="32"/>
     </row>
-    <row r="45" spans="1:13">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" s="32" t="s">
         <v>480</v>
       </c>
@@ -6959,7 +7003,7 @@
       </c>
       <c r="M45" s="32"/>
     </row>
-    <row r="46" spans="1:13">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" s="32" t="s">
         <v>480</v>
       </c>
@@ -6998,7 +7042,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="47" spans="1:13">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" s="32" t="s">
         <v>480</v>
       </c>
@@ -7035,7 +7079,7 @@
       <c r="L47" s="32"/>
       <c r="M47" s="32"/>
     </row>
-    <row r="48" spans="1:13">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" s="32" t="s">
         <v>480</v>
       </c>
@@ -7074,7 +7118,7 @@
       </c>
       <c r="M48" s="32"/>
     </row>
-    <row r="49" spans="1:13" ht="13.15" customHeight="1">
+    <row r="49" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="32" t="s">
         <v>480</v>
       </c>
@@ -7103,13 +7147,13 @@
         <v>543</v>
       </c>
       <c r="J49" s="32"/>
-      <c r="K49" s="44" t="s">
+      <c r="K49" s="43" t="s">
         <v>544</v>
       </c>
       <c r="L49" s="32"/>
       <c r="M49" s="32"/>
     </row>
-    <row r="50" spans="1:13">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" s="32" t="s">
         <v>480</v>
       </c>
@@ -7148,7 +7192,7 @@
       </c>
       <c r="M50" s="32"/>
     </row>
-    <row r="51" spans="1:13">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" s="32" t="s">
         <v>480</v>
       </c>
@@ -7185,32 +7229,32 @@
       </c>
       <c r="M51" s="32"/>
     </row>
-    <row r="52" spans="1:13" s="48" customFormat="1" ht="15.6" customHeight="1">
-      <c r="A52" s="49" t="s">
+    <row r="52" spans="1:13" s="47" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="48" t="s">
         <v>560</v>
       </c>
-      <c r="B52" s="45"/>
-      <c r="C52" s="45"/>
-      <c r="D52" s="45"/>
-      <c r="E52" s="45"/>
-      <c r="F52" s="45"/>
-      <c r="G52" s="46" t="s">
+      <c r="B52" s="44"/>
+      <c r="C52" s="44"/>
+      <c r="D52" s="44"/>
+      <c r="E52" s="44"/>
+      <c r="F52" s="44"/>
+      <c r="G52" s="45" t="s">
         <v>319</v>
       </c>
-      <c r="H52" s="45"/>
-      <c r="I52" s="45" t="s">
+      <c r="H52" s="44"/>
+      <c r="I52" s="44" t="s">
         <v>320</v>
       </c>
-      <c r="J52" s="67" t="s">
+      <c r="J52" s="66" t="s">
         <v>321</v>
       </c>
       <c r="K52" s="26" t="s">
         <v>322</v>
       </c>
-      <c r="L52" s="45"/>
-      <c r="M52" s="45"/>
-    </row>
-    <row r="53" spans="1:13">
+      <c r="L52" s="44"/>
+      <c r="M52" s="44"/>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" s="32" t="s">
         <v>561</v>
       </c>
@@ -7245,7 +7289,7 @@
       <c r="L53" s="32"/>
       <c r="M53" s="32"/>
     </row>
-    <row r="54" spans="1:13" ht="30.75">
+    <row r="54" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="32" t="s">
         <v>561</v>
       </c>
@@ -7271,7 +7315,7 @@
       <c r="I54" s="32" t="s">
         <v>334</v>
       </c>
-      <c r="J54" s="66" t="s">
+      <c r="J54" s="65" t="s">
         <v>335</v>
       </c>
       <c r="K54" s="38" t="s">
@@ -7280,7 +7324,7 @@
       <c r="L54" s="32"/>
       <c r="M54" s="32"/>
     </row>
-    <row r="55" spans="1:13" ht="30.75">
+    <row r="55" spans="1:13" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="32" t="s">
         <v>561</v>
       </c>
@@ -7306,7 +7350,7 @@
       <c r="I55" s="32" t="s">
         <v>334</v>
       </c>
-      <c r="J55" s="66" t="s">
+      <c r="J55" s="65" t="s">
         <v>335</v>
       </c>
       <c r="K55" s="38" t="s">
@@ -7315,7 +7359,7 @@
       <c r="L55" s="32"/>
       <c r="M55" s="32"/>
     </row>
-    <row r="56" spans="1:13">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56" s="32" t="s">
         <v>561</v>
       </c>
@@ -7352,7 +7396,7 @@
       <c r="L56" s="32"/>
       <c r="M56" s="32"/>
     </row>
-    <row r="57" spans="1:13" ht="15" thickBot="1">
+    <row r="57" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="32" t="s">
         <v>561</v>
       </c>
@@ -7377,10 +7421,10 @@
       <c r="H57" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="I57" s="45" t="s">
+      <c r="I57" s="44" t="s">
         <v>273</v>
       </c>
-      <c r="J57" s="47" t="s">
+      <c r="J57" s="46" t="s">
         <v>349</v>
       </c>
       <c r="K57" s="26" t="s">
@@ -7388,23 +7432,23 @@
       </c>
       <c r="M57" s="32"/>
     </row>
-    <row r="58" spans="1:13" s="2" customFormat="1" ht="15.6" thickBot="1">
+    <row r="58" spans="1:13" s="2" customFormat="1" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
         <v>561</v>
       </c>
-      <c r="B58" s="50" t="s">
+      <c r="B58" s="49" t="s">
         <v>65</v>
       </c>
-      <c r="C58" s="51" t="s">
+      <c r="C58" s="50" t="s">
         <v>583</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>584</v>
       </c>
-      <c r="F58" s="60" t="s">
+      <c r="F58" s="59" t="s">
         <v>585</v>
       </c>
-      <c r="G58" s="52" t="s">
+      <c r="G58" s="51" t="s">
         <v>586</v>
       </c>
       <c r="I58" s="2" t="s">
@@ -7415,7 +7459,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="59" spans="1:13">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" s="32" t="s">
         <v>561</v>
       </c>
@@ -7450,7 +7494,7 @@
       <c r="L59" s="32"/>
       <c r="M59" s="32"/>
     </row>
-    <row r="60" spans="1:13">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" s="32" t="s">
         <v>561</v>
       </c>
@@ -7489,7 +7533,7 @@
       </c>
       <c r="M60" s="32"/>
     </row>
-    <row r="61" spans="1:13">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61" s="32" t="s">
         <v>561</v>
       </c>
@@ -7526,7 +7570,7 @@
       </c>
       <c r="M61" s="32"/>
     </row>
-    <row r="62" spans="1:13" ht="16.149999999999999" customHeight="1">
+    <row r="62" spans="1:13" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="32" t="s">
         <v>561</v>
       </c>
@@ -7561,7 +7605,7 @@
       <c r="L62" s="32"/>
       <c r="M62" s="32"/>
     </row>
-    <row r="63" spans="1:13" ht="15.6" customHeight="1">
+    <row r="63" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="32" t="s">
         <v>561</v>
       </c>
@@ -7596,7 +7640,7 @@
       <c r="L63" s="32"/>
       <c r="M63" s="32"/>
     </row>
-    <row r="64" spans="1:13" ht="14.45" customHeight="1">
+    <row r="64" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="32" t="s">
         <v>561</v>
       </c>
@@ -7633,7 +7677,7 @@
       </c>
       <c r="M64" s="32"/>
     </row>
-    <row r="65" spans="1:14">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" s="32" t="s">
         <v>561</v>
       </c>
@@ -7670,7 +7714,7 @@
       </c>
       <c r="M65" s="32"/>
     </row>
-    <row r="66" spans="1:14">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="32" t="s">
         <v>561</v>
       </c>
@@ -7707,7 +7751,7 @@
       </c>
       <c r="M66" s="32"/>
     </row>
-    <row r="67" spans="1:14">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="32" t="s">
         <v>561</v>
       </c>
@@ -7744,7 +7788,7 @@
       </c>
       <c r="M67" s="32"/>
     </row>
-    <row r="68" spans="1:14" ht="24">
+    <row r="68" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="32" t="s">
         <v>561</v>
       </c>
@@ -7781,7 +7825,7 @@
       </c>
       <c r="M68" s="32"/>
     </row>
-    <row r="69" spans="1:14" ht="24">
+    <row r="69" spans="1:14" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="32" t="s">
         <v>561</v>
       </c>
@@ -7818,7 +7862,7 @@
       </c>
       <c r="M69" s="32"/>
     </row>
-    <row r="70" spans="1:14">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="32" t="s">
         <v>561</v>
       </c>
@@ -7855,44 +7899,44 @@
       </c>
       <c r="M70" s="32"/>
     </row>
-    <row r="71" spans="1:14" s="48" customFormat="1" ht="30.75">
-      <c r="A71" s="45" t="s">
+    <row r="71" spans="1:14" s="47" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="44" t="s">
         <v>561</v>
       </c>
-      <c r="B71" s="45" t="s">
+      <c r="B71" s="44" t="s">
         <v>629</v>
       </c>
-      <c r="C71" s="45" t="s">
+      <c r="C71" s="44" t="s">
         <v>434</v>
       </c>
-      <c r="D71" s="45" t="s">
+      <c r="D71" s="44" t="s">
         <v>630</v>
       </c>
-      <c r="E71" s="64" t="s">
+      <c r="E71" s="63" t="s">
         <v>436</v>
       </c>
-      <c r="F71" s="49" t="s">
+      <c r="F71" s="48" t="s">
         <v>631</v>
       </c>
-      <c r="G71" s="53"/>
-      <c r="H71" s="46" t="s">
+      <c r="G71" s="52"/>
+      <c r="H71" s="45" t="s">
         <v>632</v>
       </c>
-      <c r="I71" s="54" t="s">
+      <c r="I71" s="53" t="s">
         <v>633</v>
       </c>
-      <c r="J71" s="64" t="s">
+      <c r="J71" s="63" t="s">
         <v>436</v>
       </c>
       <c r="K71" s="26" t="s">
         <v>627</v>
       </c>
-      <c r="L71" s="45" t="s">
+      <c r="L71" s="44" t="s">
         <v>634</v>
       </c>
-      <c r="M71" s="45"/>
-    </row>
-    <row r="72" spans="1:14" ht="30.75">
+      <c r="M71" s="44"/>
+    </row>
+    <row r="72" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="32" t="s">
         <v>561</v>
       </c>
@@ -7920,7 +7964,7 @@
       <c r="I72" s="32" t="s">
         <v>637</v>
       </c>
-      <c r="J72" s="56" t="s">
+      <c r="J72" s="55" t="s">
         <v>93</v>
       </c>
       <c r="K72" s="25" t="s">
@@ -7931,7 +7975,7 @@
       </c>
       <c r="M72" s="32"/>
     </row>
-    <row r="73" spans="1:14" ht="15">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="32" t="s">
         <v>561</v>
       </c>
@@ -7970,7 +8014,7 @@
       </c>
       <c r="M73" s="32"/>
     </row>
-    <row r="74" spans="1:14" ht="17.25" customHeight="1">
+    <row r="74" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="32" t="s">
         <v>561</v>
       </c>
@@ -8005,35 +8049,35 @@
       <c r="L74" s="32"/>
       <c r="M74" s="32"/>
     </row>
-    <row r="75" spans="1:14" s="57" customFormat="1" ht="15">
-      <c r="A75" s="57" t="s">
+    <row r="75" spans="1:14" s="56" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="56" t="s">
         <v>561</v>
       </c>
       <c r="B75" s="32" t="s">
         <v>65</v>
       </c>
       <c r="C75" s="32"/>
-      <c r="D75" s="57" t="s">
+      <c r="D75" s="56" t="s">
         <v>649</v>
       </c>
       <c r="E75" s="2"/>
-      <c r="F75" s="57" t="s">
+      <c r="F75" s="56" t="s">
         <v>650</v>
       </c>
-      <c r="G75" s="58" t="s">
+      <c r="G75" s="57" t="s">
         <v>651</v>
       </c>
-      <c r="I75" s="57" t="s">
+      <c r="I75" s="56" t="s">
         <v>652</v>
       </c>
-      <c r="J75" s="55" t="s">
+      <c r="J75" s="54" t="s">
         <v>653</v>
       </c>
-      <c r="K75" s="59" t="s">
+      <c r="K75" s="58" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="76" spans="1:14" ht="48">
+    <row r="76" spans="1:14" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="32" t="s">
         <v>561</v>
       </c>
@@ -8056,10 +8100,10 @@
         <v>468</v>
       </c>
       <c r="H76" s="32"/>
-      <c r="I76" s="62" t="s">
+      <c r="I76" s="61" t="s">
         <v>469</v>
       </c>
-      <c r="J76" s="61" t="s">
+      <c r="J76" s="60" t="s">
         <v>470</v>
       </c>
       <c r="K76" s="38" t="s">
@@ -8070,7 +8114,7 @@
       </c>
       <c r="M76" s="32"/>
     </row>
-    <row r="77" spans="1:14" ht="15">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" s="32" t="s">
         <v>561</v>
       </c>
@@ -8107,7 +8151,7 @@
       <c r="L77" s="32"/>
       <c r="M77" s="32"/>
     </row>
-    <row r="78" spans="1:14">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" s="32"/>
       <c r="B78" s="32"/>
       <c r="C78" s="32"/>
@@ -8122,7 +8166,7 @@
       <c r="L78" s="32"/>
       <c r="M78" s="32"/>
     </row>
-    <row r="79" spans="1:14">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" s="35"/>
       <c r="B79" s="32"/>
       <c r="C79" s="32"/>
@@ -8140,7 +8184,7 @@
       <c r="M79" s="32"/>
       <c r="N79" s="32"/>
     </row>
-    <row r="80" spans="1:14">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" s="36"/>
       <c r="B80" s="32"/>
       <c r="C80" s="32"/>
@@ -8155,7 +8199,7 @@
       <c r="M80" s="32"/>
       <c r="N80" s="32"/>
     </row>
-    <row r="81" spans="1:14">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81" s="32"/>
       <c r="B81" s="32"/>
       <c r="C81" s="32"/>
@@ -8170,324 +8214,324 @@
       <c r="M81" s="32"/>
       <c r="N81" s="32"/>
     </row>
-    <row r="82" spans="1:14">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
       <c r="J82" s="32"/>
       <c r="L82" s="32"/>
       <c r="M82" s="32"/>
     </row>
-    <row r="83" spans="1:14">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
       <c r="J83" s="32"/>
       <c r="L83" s="32"/>
       <c r="M83" s="32"/>
     </row>
-    <row r="84" spans="1:14">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
       <c r="J84" s="32"/>
       <c r="L84" s="32"/>
       <c r="M84" s="32"/>
     </row>
-    <row r="85" spans="1:14">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="J85" s="32"/>
       <c r="L85" s="32"/>
       <c r="M85" s="32"/>
     </row>
-    <row r="86" spans="1:14">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
       <c r="J86" s="32"/>
       <c r="L86" s="32"/>
       <c r="M86" s="32"/>
     </row>
-    <row r="87" spans="1:14">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
       <c r="J87" s="32"/>
       <c r="L87" s="32"/>
       <c r="M87" s="32"/>
     </row>
-    <row r="88" spans="1:14">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
       <c r="J88" s="32"/>
       <c r="L88" s="32"/>
       <c r="M88" s="32"/>
     </row>
-    <row r="89" spans="1:14">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
       <c r="J89" s="32"/>
       <c r="L89" s="32"/>
       <c r="M89" s="32"/>
     </row>
-    <row r="90" spans="1:14">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
       <c r="J90" s="32"/>
       <c r="L90" s="32"/>
       <c r="M90" s="32"/>
     </row>
-    <row r="91" spans="1:14">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
       <c r="J91" s="32"/>
       <c r="L91" s="32"/>
       <c r="M91" s="32"/>
     </row>
-    <row r="92" spans="1:14">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
       <c r="J92" s="32"/>
       <c r="L92" s="32"/>
       <c r="M92" s="32"/>
     </row>
-    <row r="93" spans="1:14">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
       <c r="J93" s="32"/>
       <c r="L93" s="32"/>
       <c r="M93" s="32"/>
     </row>
-    <row r="94" spans="1:14">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
       <c r="J94" s="32"/>
       <c r="L94" s="32"/>
       <c r="M94" s="32"/>
     </row>
-    <row r="95" spans="1:14">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
       <c r="J95" s="32"/>
       <c r="L95" s="32"/>
       <c r="M95" s="32"/>
     </row>
-    <row r="96" spans="1:14">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
       <c r="J96" s="32"/>
       <c r="L96" s="32"/>
       <c r="M96" s="32"/>
     </row>
-    <row r="97" spans="10:13">
+    <row r="97" spans="10:13" x14ac:dyDescent="0.3">
       <c r="J97" s="32"/>
       <c r="L97" s="32"/>
       <c r="M97" s="32"/>
     </row>
-    <row r="98" spans="10:13">
+    <row r="98" spans="10:13" x14ac:dyDescent="0.3">
       <c r="J98" s="32"/>
       <c r="L98" s="32"/>
       <c r="M98" s="32"/>
     </row>
-    <row r="99" spans="10:13">
+    <row r="99" spans="10:13" x14ac:dyDescent="0.3">
       <c r="J99" s="32"/>
       <c r="L99" s="32"/>
       <c r="M99" s="32"/>
     </row>
-    <row r="100" spans="10:13">
+    <row r="100" spans="10:13" x14ac:dyDescent="0.3">
       <c r="J100" s="32"/>
       <c r="L100" s="32"/>
       <c r="M100" s="32"/>
     </row>
-    <row r="101" spans="10:13">
+    <row r="101" spans="10:13" x14ac:dyDescent="0.3">
       <c r="J101" s="32"/>
       <c r="L101" s="32"/>
       <c r="M101" s="32"/>
     </row>
-    <row r="102" spans="10:13">
+    <row r="102" spans="10:13" x14ac:dyDescent="0.3">
       <c r="J102" s="32"/>
       <c r="L102" s="32"/>
       <c r="M102" s="32"/>
     </row>
-    <row r="103" spans="10:13">
+    <row r="103" spans="10:13" x14ac:dyDescent="0.3">
       <c r="J103" s="32"/>
       <c r="L103" s="32"/>
       <c r="M103" s="32"/>
     </row>
-    <row r="104" spans="10:13">
+    <row r="104" spans="10:13" x14ac:dyDescent="0.3">
       <c r="J104" s="32"/>
       <c r="L104" s="32"/>
       <c r="M104" s="32"/>
     </row>
-    <row r="105" spans="10:13">
+    <row r="105" spans="10:13" x14ac:dyDescent="0.3">
       <c r="J105" s="32"/>
       <c r="L105" s="32"/>
       <c r="M105" s="32"/>
     </row>
-    <row r="106" spans="10:13">
+    <row r="106" spans="10:13" x14ac:dyDescent="0.3">
       <c r="J106" s="32"/>
       <c r="L106" s="32"/>
       <c r="M106" s="32"/>
     </row>
-    <row r="107" spans="10:13">
+    <row r="107" spans="10:13" x14ac:dyDescent="0.3">
       <c r="J107" s="32"/>
       <c r="L107" s="32"/>
       <c r="M107" s="32"/>
     </row>
-    <row r="108" spans="10:13">
+    <row r="108" spans="10:13" x14ac:dyDescent="0.3">
       <c r="J108" s="32"/>
     </row>
-    <row r="109" spans="10:13">
+    <row r="109" spans="10:13" x14ac:dyDescent="0.3">
       <c r="J109" s="32"/>
     </row>
-    <row r="110" spans="10:13">
+    <row r="110" spans="10:13" x14ac:dyDescent="0.3">
       <c r="J110" s="32"/>
     </row>
-    <row r="111" spans="10:13">
+    <row r="111" spans="10:13" x14ac:dyDescent="0.3">
       <c r="J111" s="32"/>
     </row>
-    <row r="112" spans="10:13">
+    <row r="112" spans="10:13" x14ac:dyDescent="0.3">
       <c r="J112" s="32"/>
     </row>
-    <row r="113" spans="10:10">
+    <row r="113" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J113" s="32"/>
     </row>
-    <row r="114" spans="10:10">
+    <row r="114" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J114" s="32"/>
     </row>
-    <row r="115" spans="10:10">
+    <row r="115" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J115" s="32"/>
     </row>
-    <row r="116" spans="10:10">
+    <row r="116" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J116" s="32"/>
     </row>
-    <row r="117" spans="10:10">
+    <row r="117" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J117" s="32"/>
     </row>
-    <row r="118" spans="10:10">
+    <row r="118" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J118" s="32"/>
     </row>
-    <row r="119" spans="10:10">
+    <row r="119" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J119" s="32"/>
     </row>
-    <row r="120" spans="10:10">
+    <row r="120" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J120" s="32"/>
     </row>
-    <row r="121" spans="10:10">
+    <row r="121" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J121" s="32"/>
     </row>
-    <row r="122" spans="10:10">
+    <row r="122" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J122" s="32"/>
     </row>
-    <row r="123" spans="10:10">
+    <row r="123" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J123" s="32"/>
     </row>
-    <row r="124" spans="10:10">
+    <row r="124" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J124" s="32"/>
     </row>
-    <row r="125" spans="10:10">
+    <row r="125" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J125" s="32"/>
     </row>
-    <row r="126" spans="10:10">
+    <row r="126" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J126" s="32"/>
     </row>
-    <row r="127" spans="10:10">
+    <row r="127" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J127" s="32"/>
     </row>
-    <row r="128" spans="10:10">
+    <row r="128" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J128" s="32"/>
     </row>
-    <row r="129" spans="10:10">
+    <row r="129" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J129" s="32"/>
     </row>
-    <row r="130" spans="10:10">
+    <row r="130" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J130" s="32"/>
     </row>
-    <row r="131" spans="10:10">
+    <row r="131" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J131" s="32"/>
     </row>
-    <row r="132" spans="10:10">
+    <row r="132" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J132" s="32"/>
     </row>
-    <row r="133" spans="10:10">
+    <row r="133" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J133" s="32"/>
     </row>
-    <row r="134" spans="10:10">
+    <row r="134" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J134" s="32"/>
     </row>
-    <row r="135" spans="10:10">
+    <row r="135" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J135" s="32"/>
     </row>
-    <row r="136" spans="10:10">
+    <row r="136" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J136" s="32"/>
     </row>
-    <row r="137" spans="10:10">
+    <row r="137" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J137" s="32"/>
     </row>
-    <row r="138" spans="10:10">
+    <row r="138" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J138" s="32"/>
     </row>
-    <row r="139" spans="10:10">
+    <row r="139" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J139" s="32"/>
     </row>
-    <row r="140" spans="10:10">
+    <row r="140" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J140" s="32"/>
     </row>
-    <row r="141" spans="10:10">
+    <row r="141" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J141" s="32"/>
     </row>
-    <row r="142" spans="10:10">
+    <row r="142" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J142" s="32"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G3" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
-    <hyperlink ref="G4" r:id="rId2" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
-    <hyperlink ref="G5" r:id="rId3" xr:uid="{00000000-0004-0000-0200-000002000000}"/>
-    <hyperlink ref="G6" r:id="rId4" xr:uid="{00000000-0004-0000-0200-000003000000}"/>
-    <hyperlink ref="G7" r:id="rId5" xr:uid="{00000000-0004-0000-0200-000004000000}"/>
-    <hyperlink ref="G8" r:id="rId6" xr:uid="{00000000-0004-0000-0200-000005000000}"/>
-    <hyperlink ref="G9" r:id="rId7" xr:uid="{00000000-0004-0000-0200-000006000000}"/>
-    <hyperlink ref="G10" r:id="rId8" xr:uid="{00000000-0004-0000-0200-000007000000}"/>
-    <hyperlink ref="G15" r:id="rId9" xr:uid="{00000000-0004-0000-0200-000008000000}"/>
-    <hyperlink ref="G16" r:id="rId10" xr:uid="{00000000-0004-0000-0200-000009000000}"/>
-    <hyperlink ref="G17" r:id="rId11" xr:uid="{00000000-0004-0000-0200-00000A000000}"/>
-    <hyperlink ref="G18" r:id="rId12" xr:uid="{00000000-0004-0000-0200-00000B000000}"/>
-    <hyperlink ref="G21" r:id="rId13" xr:uid="{00000000-0004-0000-0200-00000C000000}"/>
-    <hyperlink ref="G23" r:id="rId14" xr:uid="{00000000-0004-0000-0200-00000D000000}"/>
-    <hyperlink ref="G31" r:id="rId15" xr:uid="{00000000-0004-0000-0200-00000E000000}"/>
-    <hyperlink ref="G36" r:id="rId16" xr:uid="{00000000-0004-0000-0200-00000F000000}"/>
-    <hyperlink ref="G37" r:id="rId17" xr:uid="{00000000-0004-0000-0200-000010000000}"/>
-    <hyperlink ref="G46" r:id="rId18" xr:uid="{00000000-0004-0000-0200-000011000000}"/>
-    <hyperlink ref="G52" r:id="rId19" xr:uid="{00000000-0004-0000-0200-000012000000}"/>
-    <hyperlink ref="G54" r:id="rId20" xr:uid="{00000000-0004-0000-0200-000013000000}"/>
-    <hyperlink ref="G55" r:id="rId21" xr:uid="{00000000-0004-0000-0200-000014000000}"/>
-    <hyperlink ref="G57" r:id="rId22" display="http://purl.obolibrary.org/obo/NCIT_C60776" xr:uid="{00000000-0004-0000-0200-000015000000}"/>
-    <hyperlink ref="G59" r:id="rId23" xr:uid="{00000000-0004-0000-0200-000016000000}"/>
-    <hyperlink ref="G61" r:id="rId24" xr:uid="{00000000-0004-0000-0200-000017000000}"/>
-    <hyperlink ref="G66" r:id="rId25" xr:uid="{00000000-0004-0000-0200-000018000000}"/>
-    <hyperlink ref="G67" r:id="rId26" xr:uid="{00000000-0004-0000-0200-000019000000}"/>
-    <hyperlink ref="G68" r:id="rId27" xr:uid="{00000000-0004-0000-0200-00001A000000}"/>
-    <hyperlink ref="G69" r:id="rId28" xr:uid="{00000000-0004-0000-0200-00001B000000}"/>
-    <hyperlink ref="G74" r:id="rId29" xr:uid="{00000000-0004-0000-0200-00001C000000}"/>
-    <hyperlink ref="G76" r:id="rId30" xr:uid="{00000000-0004-0000-0200-00001D000000}"/>
-    <hyperlink ref="H11" r:id="rId31" xr:uid="{00000000-0004-0000-0200-00001E000000}"/>
-    <hyperlink ref="H12" r:id="rId32" xr:uid="{00000000-0004-0000-0200-00001F000000}"/>
-    <hyperlink ref="H13" r:id="rId33" xr:uid="{00000000-0004-0000-0200-000020000000}"/>
-    <hyperlink ref="H14" r:id="rId34" xr:uid="{00000000-0004-0000-0200-000021000000}"/>
-    <hyperlink ref="H19" r:id="rId35" xr:uid="{00000000-0004-0000-0200-000022000000}"/>
-    <hyperlink ref="H22" r:id="rId36" xr:uid="{00000000-0004-0000-0200-000023000000}"/>
-    <hyperlink ref="H24" r:id="rId37" xr:uid="{00000000-0004-0000-0200-000024000000}"/>
-    <hyperlink ref="H25" r:id="rId38" xr:uid="{00000000-0004-0000-0200-000025000000}"/>
-    <hyperlink ref="H26" r:id="rId39" xr:uid="{00000000-0004-0000-0200-000026000000}"/>
-    <hyperlink ref="H27" r:id="rId40" xr:uid="{00000000-0004-0000-0200-000027000000}"/>
-    <hyperlink ref="H28" r:id="rId41" xr:uid="{00000000-0004-0000-0200-000028000000}"/>
-    <hyperlink ref="H29" r:id="rId42" xr:uid="{00000000-0004-0000-0200-000029000000}"/>
-    <hyperlink ref="H32" r:id="rId43" xr:uid="{00000000-0004-0000-0200-00002A000000}"/>
-    <hyperlink ref="H33" r:id="rId44" xr:uid="{00000000-0004-0000-0200-00002B000000}"/>
-    <hyperlink ref="H34" r:id="rId45" xr:uid="{00000000-0004-0000-0200-00002C000000}"/>
-    <hyperlink ref="H35" r:id="rId46" xr:uid="{00000000-0004-0000-0200-00002D000000}"/>
-    <hyperlink ref="H38" r:id="rId47" xr:uid="{00000000-0004-0000-0200-00002E000000}"/>
-    <hyperlink ref="H39" r:id="rId48" xr:uid="{00000000-0004-0000-0200-00002F000000}"/>
-    <hyperlink ref="H40" r:id="rId49" xr:uid="{00000000-0004-0000-0200-000030000000}"/>
-    <hyperlink ref="H41" r:id="rId50" xr:uid="{00000000-0004-0000-0200-000031000000}"/>
-    <hyperlink ref="H42" r:id="rId51" xr:uid="{00000000-0004-0000-0200-000032000000}"/>
-    <hyperlink ref="H43" r:id="rId52" xr:uid="{00000000-0004-0000-0200-000033000000}"/>
-    <hyperlink ref="H44" r:id="rId53" xr:uid="{00000000-0004-0000-0200-000034000000}"/>
-    <hyperlink ref="H45" r:id="rId54" xr:uid="{00000000-0004-0000-0200-000035000000}"/>
-    <hyperlink ref="H47" r:id="rId55" xr:uid="{00000000-0004-0000-0200-000036000000}"/>
-    <hyperlink ref="H48" r:id="rId56" xr:uid="{00000000-0004-0000-0200-000037000000}"/>
-    <hyperlink ref="H49" r:id="rId57" display="https://www.google.com/search?q=http://purl.obolibrary.org/obo/RO_0002351" xr:uid="{00000000-0004-0000-0200-000038000000}"/>
-    <hyperlink ref="H50" r:id="rId58" xr:uid="{00000000-0004-0000-0200-000039000000}"/>
-    <hyperlink ref="H51" r:id="rId59" xr:uid="{00000000-0004-0000-0200-00003A000000}"/>
-    <hyperlink ref="H53" r:id="rId60" xr:uid="{00000000-0004-0000-0200-00003B000000}"/>
-    <hyperlink ref="H56" r:id="rId61" xr:uid="{00000000-0004-0000-0200-00003C000000}"/>
-    <hyperlink ref="H57" r:id="rId62" xr:uid="{00000000-0004-0000-0200-00003D000000}"/>
-    <hyperlink ref="H60" r:id="rId63" xr:uid="{00000000-0004-0000-0200-00003E000000}"/>
-    <hyperlink ref="H62" r:id="rId64" xr:uid="{00000000-0004-0000-0200-00003F000000}"/>
-    <hyperlink ref="H63" r:id="rId65" xr:uid="{00000000-0004-0000-0200-000040000000}"/>
-    <hyperlink ref="H64" r:id="rId66" xr:uid="{00000000-0004-0000-0200-000041000000}"/>
-    <hyperlink ref="H65" r:id="rId67" xr:uid="{00000000-0004-0000-0200-000042000000}"/>
-    <hyperlink ref="H66" r:id="rId68" xr:uid="{00000000-0004-0000-0200-000043000000}"/>
-    <hyperlink ref="H67" r:id="rId69" xr:uid="{00000000-0004-0000-0200-000044000000}"/>
-    <hyperlink ref="H70" r:id="rId70" xr:uid="{00000000-0004-0000-0200-000045000000}"/>
-    <hyperlink ref="H71" r:id="rId71" xr:uid="{00000000-0004-0000-0200-000046000000}"/>
-    <hyperlink ref="H72" r:id="rId72" xr:uid="{00000000-0004-0000-0200-000047000000}"/>
-    <hyperlink ref="H73" r:id="rId73" xr:uid="{00000000-0004-0000-0200-000048000000}"/>
-    <hyperlink ref="H77" r:id="rId74" xr:uid="{00000000-0004-0000-0200-000049000000}"/>
-    <hyperlink ref="L9" r:id="rId75" location="contact-information" display="https://github.com/BBMRI-ERIC/miabis/blob/master/Structured-data-and-lists.md - contact-information" xr:uid="{00000000-0004-0000-0200-00004A000000}"/>
-    <hyperlink ref="L20" r:id="rId76" location="contact-information" display="https://github.com/BBMRI-ERIC/miabis/blob/master/all structured data.md - contact-information" xr:uid="{00000000-0004-0000-0200-00004B000000}"/>
-    <hyperlink ref="L31" r:id="rId77" location="disease" display="https://github.com/BBMRI-ERIC/miabis/blob/master/all structured data.md - disease" xr:uid="{00000000-0004-0000-0200-00004C000000}"/>
-    <hyperlink ref="L46" r:id="rId78" location="contact-information" display="https://github.com/BBMRI-ERIC/miabis/blob/master/all structured data.md - contact-information" xr:uid="{00000000-0004-0000-0200-00004D000000}"/>
-    <hyperlink ref="K28" r:id="rId79" display="http://purl.obolibrary.org/obo/IAO_0000030" xr:uid="{00000000-0004-0000-0200-00004E000000}"/>
-    <hyperlink ref="G30" r:id="rId80" xr:uid="{00000000-0004-0000-0200-00004F000000}"/>
-    <hyperlink ref="K49" r:id="rId81" display="http://purl.obolibrary.org/obo/IAO_0000030" xr:uid="{00000000-0004-0000-0200-000050000000}"/>
+    <hyperlink ref="G3" r:id="rId1"/>
+    <hyperlink ref="G4" r:id="rId2"/>
+    <hyperlink ref="G5" r:id="rId3"/>
+    <hyperlink ref="G6" r:id="rId4"/>
+    <hyperlink ref="G7" r:id="rId5"/>
+    <hyperlink ref="G8" r:id="rId6"/>
+    <hyperlink ref="G9" r:id="rId7"/>
+    <hyperlink ref="G10" r:id="rId8"/>
+    <hyperlink ref="G15" r:id="rId9"/>
+    <hyperlink ref="G16" r:id="rId10"/>
+    <hyperlink ref="G17" r:id="rId11"/>
+    <hyperlink ref="G18" r:id="rId12"/>
+    <hyperlink ref="G21" r:id="rId13"/>
+    <hyperlink ref="G23" r:id="rId14"/>
+    <hyperlink ref="G31" r:id="rId15"/>
+    <hyperlink ref="G36" r:id="rId16"/>
+    <hyperlink ref="G37" r:id="rId17"/>
+    <hyperlink ref="G46" r:id="rId18"/>
+    <hyperlink ref="G52" r:id="rId19"/>
+    <hyperlink ref="G54" r:id="rId20"/>
+    <hyperlink ref="G55" r:id="rId21"/>
+    <hyperlink ref="G57" r:id="rId22" display="http://purl.obolibrary.org/obo/NCIT_C60776"/>
+    <hyperlink ref="G59" r:id="rId23"/>
+    <hyperlink ref="G61" r:id="rId24"/>
+    <hyperlink ref="G66" r:id="rId25"/>
+    <hyperlink ref="G67" r:id="rId26"/>
+    <hyperlink ref="G68" r:id="rId27"/>
+    <hyperlink ref="G69" r:id="rId28"/>
+    <hyperlink ref="G74" r:id="rId29"/>
+    <hyperlink ref="G76" r:id="rId30"/>
+    <hyperlink ref="H11" r:id="rId31"/>
+    <hyperlink ref="H12" r:id="rId32"/>
+    <hyperlink ref="H13" r:id="rId33"/>
+    <hyperlink ref="H14" r:id="rId34"/>
+    <hyperlink ref="H19" r:id="rId35"/>
+    <hyperlink ref="H22" r:id="rId36"/>
+    <hyperlink ref="H24" r:id="rId37"/>
+    <hyperlink ref="H25" r:id="rId38"/>
+    <hyperlink ref="H26" r:id="rId39"/>
+    <hyperlink ref="H27" r:id="rId40"/>
+    <hyperlink ref="H28" r:id="rId41"/>
+    <hyperlink ref="H29" r:id="rId42"/>
+    <hyperlink ref="H32" r:id="rId43"/>
+    <hyperlink ref="H33" r:id="rId44"/>
+    <hyperlink ref="H34" r:id="rId45"/>
+    <hyperlink ref="H35" r:id="rId46"/>
+    <hyperlink ref="H38" r:id="rId47"/>
+    <hyperlink ref="H39" r:id="rId48"/>
+    <hyperlink ref="H40" r:id="rId49"/>
+    <hyperlink ref="H41" r:id="rId50"/>
+    <hyperlink ref="H42" r:id="rId51"/>
+    <hyperlink ref="H43" r:id="rId52"/>
+    <hyperlink ref="H44" r:id="rId53"/>
+    <hyperlink ref="H45" r:id="rId54"/>
+    <hyperlink ref="H47" r:id="rId55"/>
+    <hyperlink ref="H48" r:id="rId56"/>
+    <hyperlink ref="H49" r:id="rId57" display="https://www.google.com/search?q=http://purl.obolibrary.org/obo/RO_0002351"/>
+    <hyperlink ref="H50" r:id="rId58"/>
+    <hyperlink ref="H51" r:id="rId59"/>
+    <hyperlink ref="H53" r:id="rId60"/>
+    <hyperlink ref="H56" r:id="rId61"/>
+    <hyperlink ref="H57" r:id="rId62"/>
+    <hyperlink ref="H60" r:id="rId63"/>
+    <hyperlink ref="H62" r:id="rId64"/>
+    <hyperlink ref="H63" r:id="rId65"/>
+    <hyperlink ref="H64" r:id="rId66"/>
+    <hyperlink ref="H65" r:id="rId67"/>
+    <hyperlink ref="H66" r:id="rId68"/>
+    <hyperlink ref="H67" r:id="rId69"/>
+    <hyperlink ref="H70" r:id="rId70"/>
+    <hyperlink ref="H71" r:id="rId71"/>
+    <hyperlink ref="H72" r:id="rId72"/>
+    <hyperlink ref="H73" r:id="rId73"/>
+    <hyperlink ref="H77" r:id="rId74"/>
+    <hyperlink ref="L9" r:id="rId75" location="contact-information" display="https://github.com/BBMRI-ERIC/miabis/blob/master/Structured-data-and-lists.md - contact-information"/>
+    <hyperlink ref="L20" r:id="rId76" location="contact-information" display="https://github.com/BBMRI-ERIC/miabis/blob/master/all structured data.md - contact-information"/>
+    <hyperlink ref="L31" r:id="rId77" location="disease" display="https://github.com/BBMRI-ERIC/miabis/blob/master/all structured data.md - disease"/>
+    <hyperlink ref="L46" r:id="rId78" location="contact-information" display="https://github.com/BBMRI-ERIC/miabis/blob/master/all structured data.md - contact-information"/>
+    <hyperlink ref="K28" r:id="rId79" display="http://purl.obolibrary.org/obo/IAO_0000030"/>
+    <hyperlink ref="G30" r:id="rId80"/>
+    <hyperlink ref="K49" r:id="rId81" display="http://purl.obolibrary.org/obo/IAO_0000030"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId82"/>
@@ -8495,14 +8539,21 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:L79"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M119"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="12" max="12" width="41.7109375" customWidth="1"/>
+    <col min="1" max="1" width="48.77734375" customWidth="1"/>
+    <col min="2" max="2" width="39.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="39.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="37" customWidth="1"/>
+    <col min="6" max="6" width="39.44140625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="20.88671875" customWidth="1"/>
+    <col min="12" max="12" width="41.6640625" style="47" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>173</v>
       </c>
@@ -8521,355 +8572,1477 @@
       <c r="F1" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="L1" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="L2" s="37"/>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="L3" s="37"/>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="L4" s="37"/>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="L5" s="37"/>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="L6" s="38" t="s">
+      <c r="L1" s="48"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="C2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="L2" s="48"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>235</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C3" t="s">
+        <v>665</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="E3" t="s">
+        <v>663</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>662</v>
       </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="L7" s="37"/>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="L8" s="37"/>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="L9" s="38" t="s">
+      <c r="L3" s="52"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>663</v>
       </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="L10" s="37"/>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="L11" s="32"/>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="L12" s="32"/>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="L13" s="37"/>
-    </row>
-    <row r="14" spans="1:12">
-      <c r="L14" s="37"/>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="L15" s="37"/>
-    </row>
-    <row r="16" spans="1:12">
-      <c r="L16" s="38" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="17" spans="12:12">
-      <c r="L17" s="38" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="18" spans="12:12">
-      <c r="L18" s="38" t="s">
+      <c r="B4" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="C4" t="s">
+        <v>667</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="E4" t="s">
         <v>666</v>
       </c>
-    </row>
-    <row r="19" spans="12:12">
-      <c r="L19" s="37"/>
-    </row>
-    <row r="20" spans="12:12">
-      <c r="L20" s="38" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="21" spans="12:12">
-      <c r="L21" s="38" t="s">
+      <c r="F4" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="L4" s="52"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>671</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C5" t="s">
+        <v>669</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="E5" t="s">
+        <v>663</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="L5" s="52"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>281</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C6" t="s">
+        <v>684</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="E6" t="s">
+        <v>663</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="L6" s="52"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>663</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="C7" t="s">
+        <v>685</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="E7" s="32" t="s">
+        <v>291</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="L7" s="52"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>663</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="C8" t="s">
+        <v>685</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="E8" s="32" t="s">
+        <v>299</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="L8" s="52"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>663</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="C9" t="s">
+        <v>685</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="E9" s="32" t="s">
+        <v>307</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="L9" s="52"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="32" t="s">
+        <v>315</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="C10" t="s">
+        <v>688</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="E10" t="s">
+        <v>663</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="L10" s="52"/>
+    </row>
+    <row r="11" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="32"/>
+      <c r="L11" s="52"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="10" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>320</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="C13" t="s">
+        <v>199</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="E13" t="s">
+        <v>675</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>334</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="C14" t="s">
+        <v>179</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E14" t="s">
+        <v>320</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>320</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="C15" t="s">
         <v>667</v>
       </c>
-    </row>
-    <row r="22" spans="12:12">
-      <c r="L22" s="38" t="s">
+      <c r="D15" s="1" t="s">
         <v>668</v>
       </c>
-    </row>
-    <row r="23" spans="12:12">
-      <c r="L23" s="38" t="s">
+      <c r="E15" t="s">
+        <v>343</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>320</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="C16" t="s">
+        <v>179</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E16" t="s">
+        <v>671</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>355</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="C17" t="s">
+        <v>684</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="E17" t="s">
+        <v>320</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>102</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C18" t="s">
+        <v>179</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E18" t="s">
+        <v>320</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>320</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="C19" t="s">
+        <v>202</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="E19" t="s">
+        <v>366</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>320</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="C20" t="s">
+        <v>682</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="E20" t="s">
+        <v>375</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="L20" s="46"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>320</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="C21" t="s">
+        <v>682</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="E21" t="s">
+        <v>381</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="L21" s="46"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>320</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="C22" t="s">
+        <v>678</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="E22" t="s">
+        <v>388</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="L22" s="52"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>320</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="C23" t="s">
+        <v>678</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="E23" t="s">
+        <v>396</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="L23" s="52"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>320</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="C24" s="32" t="s">
+        <v>402</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="L24" s="52"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>320</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="C25" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L25" s="52"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>320</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="C26" t="s">
+        <v>181</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="E26" t="s">
+        <v>41</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>423</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C27" t="s">
+        <v>702</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="E27" t="s">
+        <v>320</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>431</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C28" t="s">
+        <v>692</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="E28" t="s">
+        <v>320</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>439</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="C29" t="s">
+        <v>694</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="E29" t="s">
+        <v>320</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>637</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C30" t="s">
+        <v>696</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="E30" t="s">
+        <v>320</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>320</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="C31" t="s">
+        <v>698</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="E31" t="s">
+        <v>451</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="L31" s="46"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>320</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="C32" t="s">
+        <v>700</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="E32" t="s">
+        <v>647</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>469</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="C33" t="s">
+        <v>692</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="E33" t="s">
+        <v>320</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>477</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C34" t="s">
+        <v>179</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E34" t="s">
+        <v>320</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A36" s="10" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>482</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C37" t="s">
+        <v>199</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="E37" t="s">
+        <v>490</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="L37" s="44"/>
+      <c r="M37" s="32"/>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>482</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C38" t="s">
+        <v>667</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="E38" t="s">
+        <v>507</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="L38" s="44"/>
+      <c r="M38" s="32"/>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>513</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="C39" t="s">
+        <v>673</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="E39" t="s">
+        <v>482</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="L39" s="52"/>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>482</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C40" t="s">
+        <v>690</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="E40" t="s">
+        <v>518</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="L40" s="52"/>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>671</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C41" t="s">
         <v>669</v>
       </c>
-    </row>
-    <row r="24" spans="12:12">
-      <c r="L24" s="38" t="s">
+      <c r="D41" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="E41" t="s">
+        <v>482</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="L41" s="52"/>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>531</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="C42" t="s">
+        <v>684</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="E42" t="s">
+        <v>482</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="L42" s="52"/>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>482</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C43" t="s">
+        <v>698</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="E43" t="s">
+        <v>537</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="L43" s="46"/>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>482</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C44" t="s">
+        <v>674</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="L44" s="52"/>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A45" s="32" t="s">
+        <v>550</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="C45" t="s">
+        <v>179</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E45" t="s">
+        <v>482</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="L45" s="52"/>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>482</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C46" s="32" t="s">
+        <v>676</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="L46" s="46"/>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A47" s="44"/>
+      <c r="L47" s="52"/>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A48" s="48" t="s">
+        <v>560</v>
+      </c>
+      <c r="L48" s="44"/>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>320</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="C49" t="s">
+        <v>199</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>670</v>
       </c>
-    </row>
-    <row r="25" spans="12:12">
-      <c r="L25" s="38" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="26" spans="12:12">
-      <c r="L26" s="38" t="s">
+      <c r="E49" s="32" t="s">
+        <v>565</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="L49" s="44"/>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>320</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="C50" t="s">
+        <v>667</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="E50" s="32" t="s">
+        <v>577</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="L50" s="44"/>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>334</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="C51" t="s">
+        <v>179</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E51" t="s">
+        <v>320</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>320</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="C52" t="s">
+        <v>179</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E52" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="27" spans="12:12">
-      <c r="L27" s="38" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="28" spans="12:12">
-      <c r="L28" s="37"/>
-    </row>
-    <row r="29" spans="12:12">
-      <c r="L29" s="37"/>
-    </row>
-    <row r="30" spans="12:12">
-      <c r="L30" s="38" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="31" spans="12:12">
-      <c r="L31" s="38" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="32" spans="12:12">
-      <c r="L32" s="38" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="33" spans="12:12">
-      <c r="L33" s="38" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="34" spans="12:12">
-      <c r="L34" s="38" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="35" spans="12:12">
-      <c r="L35" s="38" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="36" spans="12:12">
-      <c r="L36" s="32" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="37" spans="12:12">
-      <c r="L37" s="32" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="38" spans="12:12">
-      <c r="L38" s="38" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="39" spans="12:12">
-      <c r="L39" s="37"/>
-    </row>
-    <row r="40" spans="12:12">
-      <c r="L40" s="32" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="41" spans="12:12">
-      <c r="L41" s="32" t="s">
+      <c r="F52" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>355</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="C53" t="s">
+        <v>684</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="E53" t="s">
+        <v>320</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>102</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C54" t="s">
+        <v>179</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E54" t="s">
+        <v>320</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>320</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="C55" t="s">
+        <v>202</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="E55" t="s">
+        <v>366</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>320</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="C56" t="s">
+        <v>682</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="E56" t="s">
+        <v>375</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="L56" s="46"/>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>320</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="C57" t="s">
+        <v>682</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="E57" t="s">
+        <v>381</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="L57" s="46"/>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>320</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="C58" t="s">
+        <v>678</v>
+      </c>
+      <c r="D58" s="1" t="s">
         <v>677</v>
       </c>
-    </row>
-    <row r="42" spans="12:12">
-      <c r="L42" s="32" t="s">
+      <c r="E58" t="s">
+        <v>388</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="L58" s="52"/>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>320</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="C59" t="s">
+        <v>678</v>
+      </c>
+      <c r="D59" s="1" t="s">
         <v>677</v>
       </c>
-    </row>
-    <row r="43" spans="12:12">
-      <c r="L43" s="32" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="44" spans="12:12">
-      <c r="L44" s="38" t="s">
+      <c r="E59" t="s">
+        <v>396</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="L59" s="52"/>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>320</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="C60" s="32" t="s">
+        <v>402</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>320</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="C61" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L61" s="46"/>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>320</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>679</v>
       </c>
-    </row>
-    <row r="45" spans="12:12">
-      <c r="L45" s="38" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="46" spans="12:12">
-      <c r="L46" s="38" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="47" spans="12:12">
-      <c r="L47" s="38" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="48" spans="12:12">
-      <c r="L48" s="38" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="49" spans="12:12">
-      <c r="L49" s="38"/>
-    </row>
-    <row r="50" spans="12:12">
-      <c r="L50" s="38" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="51" spans="12:12">
-      <c r="L51" s="38"/>
-    </row>
-    <row r="52" spans="12:12">
-      <c r="L52" s="38"/>
-    </row>
-    <row r="53" spans="12:12">
-      <c r="L53" s="38" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="54" spans="12:12">
-      <c r="L54" s="38" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="55" spans="12:12">
-      <c r="L55" s="38" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="56" spans="12:12">
-      <c r="L56" s="38" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="57" spans="12:12">
-      <c r="L57" s="38" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="58" spans="12:12">
-      <c r="L58" s="38" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="59" spans="12:12">
-      <c r="L59" s="38" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="60" spans="12:12">
-      <c r="L60" s="38" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="61" spans="12:12">
-      <c r="L61" s="38" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="62" spans="12:12" ht="27">
-      <c r="L62" s="41" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="63" spans="12:12" ht="27">
-      <c r="L63" s="41" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="64" spans="12:12" ht="27">
-      <c r="L64" s="41" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="65" spans="12:12">
-      <c r="L65" s="38" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="66" spans="12:12">
-      <c r="L66" s="37"/>
-    </row>
-    <row r="67" spans="12:12">
-      <c r="L67" s="37"/>
-    </row>
-    <row r="68" spans="12:12">
-      <c r="L68" s="38" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="69" spans="12:12">
-      <c r="L69" s="38" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="70" spans="12:12">
-      <c r="L70" s="38" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="71" spans="12:12">
-      <c r="L71" s="38" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="72" spans="12:12">
-      <c r="L72" s="38" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="73" spans="12:12">
-      <c r="L73" s="38" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="74" spans="12:12">
-      <c r="L74" s="32" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="75" spans="12:12">
-      <c r="L75" s="43"/>
-    </row>
-    <row r="76" spans="12:12">
-      <c r="L76" s="32" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="77" spans="12:12">
-      <c r="L77" s="38" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="78" spans="12:12">
-      <c r="L78" s="37"/>
-    </row>
-    <row r="79" spans="12:12">
-      <c r="L79" s="38" t="s">
-        <v>15</v>
-      </c>
+      <c r="C62" t="s">
+        <v>181</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="E62" t="s">
+        <v>41</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L62" s="46"/>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>423</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C63" t="s">
+        <v>702</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="E63" t="s">
+        <v>320</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>431</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C64" t="s">
+        <v>692</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="E64" t="s">
+        <v>320</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>633</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="C65" t="s">
+        <v>694</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="E65" t="s">
+        <v>320</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>637</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C66" t="s">
+        <v>696</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="E66" t="s">
+        <v>320</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>320</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="C67" t="s">
+        <v>698</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="E67" t="s">
+        <v>451</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="L67" s="46"/>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>320</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="C68" t="s">
+        <v>700</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="E68" t="s">
+        <v>647</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>469</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="C69" t="s">
+        <v>692</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="E69" t="s">
+        <v>320</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>477</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C70" t="s">
+        <v>179</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E70" t="s">
+        <v>320</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L71" s="46"/>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L73" s="46"/>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L74" s="46"/>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L75" s="46"/>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L76" s="44"/>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L77" s="44"/>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L78" s="46"/>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L79" s="52"/>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L80" s="44"/>
+    </row>
+    <row r="81" spans="12:12" x14ac:dyDescent="0.3">
+      <c r="L81" s="44"/>
+    </row>
+    <row r="82" spans="12:12" x14ac:dyDescent="0.3">
+      <c r="L82" s="44"/>
+    </row>
+    <row r="83" spans="12:12" x14ac:dyDescent="0.3">
+      <c r="L83" s="44"/>
+    </row>
+    <row r="84" spans="12:12" x14ac:dyDescent="0.3">
+      <c r="L84" s="46"/>
+    </row>
+    <row r="85" spans="12:12" x14ac:dyDescent="0.3">
+      <c r="L85" s="46"/>
+    </row>
+    <row r="86" spans="12:12" x14ac:dyDescent="0.3">
+      <c r="L86" s="46"/>
+    </row>
+    <row r="87" spans="12:12" x14ac:dyDescent="0.3">
+      <c r="L87" s="46"/>
+    </row>
+    <row r="88" spans="12:12" x14ac:dyDescent="0.3">
+      <c r="L88" s="46"/>
+    </row>
+    <row r="89" spans="12:12" x14ac:dyDescent="0.3">
+      <c r="L89" s="46"/>
+    </row>
+    <row r="90" spans="12:12" x14ac:dyDescent="0.3">
+      <c r="L90" s="46"/>
+    </row>
+    <row r="91" spans="12:12" x14ac:dyDescent="0.3">
+      <c r="L91" s="46"/>
+    </row>
+    <row r="92" spans="12:12" x14ac:dyDescent="0.3">
+      <c r="L92" s="46"/>
+    </row>
+    <row r="93" spans="12:12" x14ac:dyDescent="0.3">
+      <c r="L93" s="46"/>
+    </row>
+    <row r="94" spans="12:12" x14ac:dyDescent="0.3">
+      <c r="L94" s="46"/>
+    </row>
+    <row r="95" spans="12:12" x14ac:dyDescent="0.3">
+      <c r="L95" s="46"/>
+    </row>
+    <row r="96" spans="12:12" x14ac:dyDescent="0.3">
+      <c r="L96" s="46"/>
+    </row>
+    <row r="97" spans="12:12" x14ac:dyDescent="0.3">
+      <c r="L97" s="46"/>
+    </row>
+    <row r="98" spans="12:12" x14ac:dyDescent="0.3">
+      <c r="L98" s="46"/>
+    </row>
+    <row r="99" spans="12:12" x14ac:dyDescent="0.3">
+      <c r="L99" s="46"/>
+    </row>
+    <row r="100" spans="12:12" x14ac:dyDescent="0.3">
+      <c r="L100" s="46"/>
+    </row>
+    <row r="101" spans="12:12" x14ac:dyDescent="0.3">
+      <c r="L101" s="46"/>
+    </row>
+    <row r="102" spans="12:12" x14ac:dyDescent="0.3">
+      <c r="L102" s="66"/>
+    </row>
+    <row r="103" spans="12:12" x14ac:dyDescent="0.3">
+      <c r="L103" s="66"/>
+    </row>
+    <row r="104" spans="12:12" x14ac:dyDescent="0.3">
+      <c r="L104" s="66"/>
+    </row>
+    <row r="105" spans="12:12" x14ac:dyDescent="0.3">
+      <c r="L105" s="46"/>
+    </row>
+    <row r="106" spans="12:12" x14ac:dyDescent="0.3">
+      <c r="L106" s="52"/>
+    </row>
+    <row r="107" spans="12:12" x14ac:dyDescent="0.3">
+      <c r="L107" s="52"/>
+    </row>
+    <row r="108" spans="12:12" x14ac:dyDescent="0.3">
+      <c r="L108" s="46"/>
+    </row>
+    <row r="109" spans="12:12" x14ac:dyDescent="0.3">
+      <c r="L109" s="46"/>
+    </row>
+    <row r="110" spans="12:12" x14ac:dyDescent="0.3">
+      <c r="L110" s="46"/>
+    </row>
+    <row r="111" spans="12:12" x14ac:dyDescent="0.3">
+      <c r="L111" s="46"/>
+    </row>
+    <row r="112" spans="12:12" x14ac:dyDescent="0.3">
+      <c r="L112" s="46"/>
+    </row>
+    <row r="113" spans="12:12" x14ac:dyDescent="0.3">
+      <c r="L113" s="46"/>
+    </row>
+    <row r="114" spans="12:12" x14ac:dyDescent="0.3">
+      <c r="L114" s="44"/>
+    </row>
+    <row r="115" spans="12:12" x14ac:dyDescent="0.3">
+      <c r="L115" s="76"/>
+    </row>
+    <row r="116" spans="12:12" x14ac:dyDescent="0.3">
+      <c r="L116" s="44"/>
+    </row>
+    <row r="117" spans="12:12" x14ac:dyDescent="0.3">
+      <c r="L117" s="46"/>
+    </row>
+    <row r="118" spans="12:12" x14ac:dyDescent="0.3">
+      <c r="L118" s="52"/>
+    </row>
+    <row r="119" spans="12:12" x14ac:dyDescent="0.3">
+      <c r="L119" s="46"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D3" r:id="rId1"/>
+    <hyperlink ref="B5" r:id="rId2"/>
+    <hyperlink ref="B41" r:id="rId3"/>
+    <hyperlink ref="C44" r:id="rId4" display="https://www.google.com/search?q=http://purl.obolibrary.org/obo/RO_0002351"/>
+    <hyperlink ref="D44" r:id="rId5" display="https://www.google.com/search?q=http://purl.obolibrary.org/obo/RO_0002351"/>
+    <hyperlink ref="B45" r:id="rId6"/>
+    <hyperlink ref="D46" r:id="rId7"/>
+    <hyperlink ref="F49" r:id="rId8"/>
+    <hyperlink ref="B49" r:id="rId9"/>
+    <hyperlink ref="B13" r:id="rId10"/>
+    <hyperlink ref="B6" r:id="rId11"/>
+    <hyperlink ref="F7" r:id="rId12"/>
+    <hyperlink ref="F8" r:id="rId13"/>
+    <hyperlink ref="F9" r:id="rId14"/>
+    <hyperlink ref="B10" r:id="rId15"/>
+    <hyperlink ref="B59:B60" r:id="rId16" display="http://purl.obolibrary.org/obo/OBIB_0000670"/>
+    <hyperlink ref="B55:B56" r:id="rId17" display="http://purl.obolibrary.org/obo/OBIB_0000670"/>
+    <hyperlink ref="B23" r:id="rId18" display="http://purl.obolibrary.org/obo/OBIB_0000670"/>
+    <hyperlink ref="B20" r:id="rId19" display="http://purl.obolibrary.org/obo/OBIB_0000670"/>
+    <hyperlink ref="B26" r:id="rId20" display="http://purl.obolibrary.org/obo/OBIB_0000670"/>
+    <hyperlink ref="B15" r:id="rId21"/>
+    <hyperlink ref="F16" r:id="rId22"/>
+    <hyperlink ref="B68" r:id="rId23" display="http://purl.obolibrary.org/obo/OBIB_0000670"/>
+    <hyperlink ref="F68" r:id="rId24"/>
+    <hyperlink ref="F52" r:id="rId25"/>
+    <hyperlink ref="B62" r:id="rId26" display="http://purl.obolibrary.org/obo/OBIB_0000670"/>
+    <hyperlink ref="D24" r:id="rId27"/>
+    <hyperlink ref="D25" r:id="rId28"/>
+    <hyperlink ref="D60" r:id="rId29"/>
+    <hyperlink ref="D61" r:id="rId30"/>
+    <hyperlink ref="B60:B61" r:id="rId31" display="http://purl.obolibrary.org/obo/OBIB_0000670"/>
+    <hyperlink ref="B24:B25" r:id="rId32" display="http://purl.obolibrary.org/obo/OBIB_0000670"/>
+    <hyperlink ref="F27" r:id="rId33" display="http://purl.obolibrary.org/obo/OBIB_0000670"/>
+    <hyperlink ref="F28" r:id="rId34" display="http://purl.obolibrary.org/obo/OBIB_0000670"/>
+    <hyperlink ref="F29" r:id="rId35" display="http://purl.obolibrary.org/obo/OBIB_0000670"/>
+    <hyperlink ref="F30" r:id="rId36" display="http://purl.obolibrary.org/obo/OBIB_0000670"/>
+    <hyperlink ref="F32" r:id="rId37"/>
+    <hyperlink ref="F33" r:id="rId38" display="http://purl.obolibrary.org/obo/OBIB_0000670"/>
+    <hyperlink ref="F34" r:id="rId39" display="http://purl.obolibrary.org/obo/OBIB_0000670"/>
+    <hyperlink ref="B50" r:id="rId40"/>
+    <hyperlink ref="F63" r:id="rId41" display="http://purl.obolibrary.org/obo/OBIB_0000670"/>
+    <hyperlink ref="F64" r:id="rId42" display="http://purl.obolibrary.org/obo/OBIB_0000670"/>
+    <hyperlink ref="F65" r:id="rId43" display="http://purl.obolibrary.org/obo/OBIB_0000670"/>
+    <hyperlink ref="F66" r:id="rId44" display="http://purl.obolibrary.org/obo/OBIB_0000670"/>
+    <hyperlink ref="F69" r:id="rId45" display="http://purl.obolibrary.org/obo/OBIB_0000670"/>
+    <hyperlink ref="F70" r:id="rId46" display="http://purl.obolibrary.org/obo/OBIB_0000670"/>
+    <hyperlink ref="B32" r:id="rId47" display="http://purl.obolibrary.org/obo/OBIB_0000670"/>
+    <hyperlink ref="B67" r:id="rId48" display="http://purl.obolibrary.org/obo/OBIB_0000670"/>
+    <hyperlink ref="B31" r:id="rId49" display="http://purl.obolibrary.org/obo/OBIB_0000670"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId50"/>
 </worksheet>
 </file>